--- a/customs_regulations.xlsx
+++ b/customs_regulations.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规范性文件" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="其他" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,13 +474,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>海关总署公告2025年第228号（关于进口马耳他野生动物源性水产品检验和卫生要求的公告）</t>
+          <t>海关总署公告2025年第201号（关于发布《进口再生纸浆检验规程》行业标准的公告）</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -494,6 +495,1886 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕201号 
+【发文机关】海关总署 
+【发布日期】2025-10-18 
+【生效日期】2025-10-18 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第201号（关于发布《进口再生纸浆检验规程》行业标准的公告）
+公告〔2025〕201号 
+现发布《进口再生纸浆检验规程》（SN/T 5939—2025）行业标准，自发布之日起实施。
+本次发布的标准文本可通过中国技术性贸易措施网站（http://www.tbtsps.cn）标准栏目查阅。
+特此公告。
+海关总署
+2025年10月18日
+公告下载链接：
+[海关总署关于发布《进口再生纸浆检验规程》行业标准的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6785281/2025102111303478599.doc)
+[海关总署关于发布《进口再生纸浆检验规程》行业标准的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6785281/2025102111304313612.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6785281/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第202号（关于进口爱沙尼亚乳品检验检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕202号 
+【发文机关】海关总署 
+【发布日期】2025-10-17 
+【生效日期】2025-10-17 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第202号（关于进口爱沙尼亚乳品检验检疫要求的公告）
+公告〔2025〕202号 
+根据我国相关法律法规和中华人民共和国海关总署与爱沙尼亚共和国地区事务和农业部有关爱沙尼亚输华乳品检验检疫要求的规定，自本公告发布之日起，允许符合检验检疫要求的爱沙尼亚乳品进口：
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
+（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
+（三）《中华人民共和国海关总署与爱沙尼亚共和国地区事务和农业部关于爱沙尼亚输华乳品检验检疫要求议定书》。
+（四）海关总署公告2021年第114号（关于明确进口乳品检验检疫有关要求的公告）。
+二、允许进口的产品
+输华乳品是指原产于爱沙尼亚，由牛乳、绵羊乳和山羊乳为主要原料加工而成的食品，包括巴氏杀菌乳、灭菌乳、调制乳、发酵乳、干酪及再制干酪、稀奶油、奶油、无水奶油、炼乳、乳粉、乳清粉、乳清蛋白粉、牛初乳粉、酪蛋白、乳矿物盐、乳基婴幼儿配方食品及其预混料（或基粉）等。
+三、生产企业要求
+输华乳品生产企业须经爱沙尼亚官方机构批准或注册，在爱沙尼亚官方监督之下于爱沙尼亚生产，且符合中国和爱沙尼亚有关动物卫生和公共卫生的要求。
+根据《中华人民共和国食品安全法》《中华人民共和国进口食品境外生产企业注册管理规定》，向中国出口乳品的生产企业应当在中国注册，未获得注册的企业生产的产品不得向中国出口。
+四、提供原料乳的奶畜要求
+为输华乳品提供原料乳的奶畜须符合以下要求：
+（一）来自符合下列条件的农场：
+1．口蹄疫检疫限制已取消至少2个月。
+2．农场没有发生过牛瘟、裂谷热、牛传染性胸膜肺炎。
+3．农场在过去12个月内没有确认的炭疽病例。
+4．爱沙尼亚从未确诊疯牛病病例，自2014年5月起，爱沙尼亚被世界动物卫生组织（WOAH）正式认可为疯牛病风险可忽略国家。
+5．农场未发现布鲁氏菌病、牛副结核病（又称Johne's disease）、结核病（tuberculosis）临床症状。
+6．农场无小反刍兽疫、痒病和羊天花。
+7．农场受爱沙尼亚官方或官方认可的第三方机构监管。
+8．农场及其周边地区未因动物疾病按WOAH法典和爱沙尼亚官方动物卫生法规规定而受到检疫限制。
+（二）动物没有饲喂过爱沙尼亚及中国禁止给动物饲喂的饲料。
+（三）执行爱沙尼亚制定的国家年度残留监控计划，并要求企业对原料乳实施检测。
+（四）根据爱沙尼亚国家残留监控计划和原料乳检测结果，输华乳品中的兽药、农药和其他有毒有害物质残留不超过中国标准设定的最高限量。
+五、证书要求
+输华乳品应随附爱沙尼亚官方签发的兽医卫生证书。
+六、食品安全要求
+输华乳品应当符合爱沙尼亚、中国法律法规的规定以及中国食品安全国家标准要求。输华乳品的生乳原料应来自爱沙尼亚，乳品原料来自经批准可向中国出口对应的乳品原料的国家（地区）。
+（一）输华乳品应当符合爱沙尼亚、中国法律法规的规定以及中国食品安全国家标准要求。
+（二）输华乳品的生乳原料应来自爱沙尼亚，乳品原料来自经批准可向中国出口对应的乳品原料的国家（地区）。
+（三）输华乳品在加工和仓储各个阶段应易于识别，不得与不符合本公告规定的乳品一起加工。
+（四）用于加工输华乳制品的生乳中不含应用抗生素期间和休药期间的乳汁、变质乳，以及初乳（用于加工牛初乳粉时除外）。
+（五）乳基婴幼儿配方食品中未添加初乳成分。
+（六）产品采用下列加工工序之一：
+1．最低温度132℃至少1秒的消毒程序（超高温UHT）；
+2．如果乳的pH低于7.0，采用最低温度72℃至少15秒的消毒程序（高温-瞬时巴氏消毒HTST）；
+3．如果乳的pH为7.0或以上时，采用HTST程序两次。
+七、包装和标识要求
+输华乳品必须用符合中国标准的全新材料包装。外包装要用中文、爱沙尼亚文及英文标明规格、产地（具体到州/省/市）、目的地、品名、重量、生产厂名称、注册编号、生产批号、储存条件、生产日期和保质期。
+内包装须符合中国相关规定，标签上应注明原产国、品名、企业注册号、生产企业名称地址和联系方式、生产日期和保质期、生产批号。
+八、存放和运输要求
+输华乳品从包装、存放到运输的全过程，均应符合卫生条件，防止受有毒有害物质的污染。货物装入集装箱后，应加施封识，封识号须在兽医卫生出口证书中注明。运输过程中不得拆开及更换包装。
+特此公告。
+海关总署
+2025年10月17日
+公告下载链接：
+[海关总署关于进口爱沙尼亚乳品检验检疫要求的公告原文.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6790984/2025102408423939475.doc)
+[海关总署关于进口爱沙尼亚乳品检验检疫要求的公告原文.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6790984/2025102408425010065.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6790984/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第203号（关于内地供港冰鲜禽肉、冷冻禽肉和冰鲜猪肉检验检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕203号 
+【发文机关】海关总署 
+【发布日期】2025-10-22 
+【生效日期】2025-10-22 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第203号（关于内地供港冰鲜禽肉、冷冻禽肉和冰鲜猪肉检验检疫要求的公告）
+公告〔2025〕203号 
+为进一步保障内地供港禽肉和猪肉安全卫生，海关总署和香港特别行政区政府环境及生态局在共同协商基础上，更新了《内地供港冰鲜禽肉的检验检疫要求》《内地供港冷冻禽肉的检验检疫要求》《内地供港冰鲜猪肉的检验检疫要求》（见附件1—3），现予以发布。
+本公告自发布之日起施行，原质检总局公告2017年第68号同步废止。
+附件：
+[1.内地供港冰鲜禽肉的检验检疫要求.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6791054/2025102408475897940.docx)
+[2.内地供港冷冻禽肉的检验检疫要求.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6791054/2025102408480870305.docx)
+[3.内地供港冰鲜猪肉的检验检疫要求.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6791054/2025102408481886664.docx)
+海关总署
+2025年10月22日
+公告正文下载链接：
+[海关总署关于内地供港冰鲜禽肉、冷冻禽肉和冰鲜猪肉检验检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6791054/2025102408482865185.doc)
+[海关总署关于内地供港冰鲜禽肉、冷冻禽肉和冰鲜猪肉检验检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6791054/2025102408483895391.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6791054/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第205号（关于进口土耳其扁桃仁检验检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕205号 
+【发文机关】海关总署 
+【发布日期】2025-10-28 
+【生效日期】2025-10-28 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第205号（关于进口土耳其扁桃仁检验检疫要求的公告）
+公告〔2025〕205号 
+根据我国法律法规和中华人民共和国海关总署（以下称中方）与土耳其共和国农业和林业部（以下称土方）有关土耳其扁桃仁输华检验检疫要求的规定，即日起，允许符合以下要求的土耳其扁桃仁进口。
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《中华人民共和国进出口商品检验法》及其实施条例；
+（四）《中华人民共和国进出口食品安全管理办法》；
+（五）《中华人民共和国海关总署与土耳其共和国农业和林业部关于土耳其扁桃仁输华检验检疫要求议定书》（以下简称《议定书》）。
+二、允许进口的产品
+允许进口的扁桃仁，是指由土耳其境内种植的扁桃（Prunus dulcis）成熟果实为原料，在土耳其境内经挑选、干燥等加工工艺制作而成的供人类食用的坚果（无论是否去壳）。
+三、食品安全要求
+土耳其扁桃仁应符合中国食品安全和植物检疫法律法规、食品安全国家标准以及《议定书》的规定。
+四、植物检疫要求
+（一）输华扁桃仁不得带有以下中方关注的检疫性有害生物：谷斑皮蠹（Trogoderma granarium）、石榴螟（Ectomyelois ceratoniae）、四纹豆象（Callosobruchus maculatus）。
+（二）输华扁桃仁应使用烘箱或烘干机等干燥机械进行脱水加工，不得带有活虫、虫卵、土壤，不得混有杂草种子、植物残体、金属异物和砂砾等杂质，加工过程中应剔除霉变粒、残壳。
+五、企业要求
+土方应按中方进口食品境外生产企业注册相关要求对土耳其输华扁桃仁生产、加工、存放单位进行检查，将符合中方要求的企业推荐给中方。中方对符合要求的企业予以注册。企业获得在华注册后，其产品方可输华。获得注册的土耳其共和国输华扁桃仁企业名单可通过海关总署网站查询。
+六、原料要求
+输华扁桃仁原料应来自经土方确认符合相关植物检疫和食品安全要求并予备案的种植企业。
+七、加工过程要求
+土方应对输华扁桃仁的原料种植、生产、加工、储存、运输、出口等过程进行指导和监管，确保符合中国和土耳其的相关食品安全和植物卫生要求，防止受到致病微生物或有毒有害物质的污染。
+八、包装、标识要求
+输华扁桃仁应使用干净、卫生、透气、新的、符合食品安全和植物检疫要求的材料包装，并在运输过程中防止发生撒漏。每一包装应以中文或英文标注“本产品输往中华人民共和国/This product is exported to the People's Republic of China”，以及产品名称、产地、生产加工企业及其在华注册编号、出口商名称和地址等可追溯信息。上述信息可以以标签形式粘贴在包装上。
+九、运输要求
+装运前，土方应对输华扁桃仁的运输工具进行检查。运输工具应符合卫生要求，不得带有检疫性有害生物或其他限定性检疫物，如杂草籽、活体昆虫、植物残体、土壤以及其他外来杂质。
+十、证书要求
+出口前，土方应对经检验检疫符合《议定书》要求的输华扁桃仁出具植物检疫证书。证书附加声明栏中应注明扁桃仁生产加工企业名称、在华注册号及“The almonds certified by this phytosanitary certificate comply with the provisions of the Protocol on Inspection and Quarantine Requirements for almonds Exported from Türkiye to China signed by China and Türkiye on October 15th, 2025. The goods are free from any quarantine pests of concern to the China Participant, such as Trogoderma granarium, Ectomyelois ceratoniae and Callosobruchus maculatus.”［该植物检疫证书所证明的扁桃仁符合中土双方于2025年10月15日签署的关于土耳其扁桃仁输华检验检疫要求议定书的规定。该批货物不带有谷斑皮蠹（Trogoderma granarium）、石榴螟（Ectomyelois ceratoniae）、四纹豆象（Callosobruchus maculatus）等中方关注的检疫性有害生物］。
+十一、进境检验检疫及不合格处理
+（一）进境检验检疫。输华扁桃仁到达中国入境口岸后，中国海关将实施检验检疫监管，合格后准予进境。
+（二）不合格处理。中方在输华扁桃仁中如发现存在违反中国食品安全和植物检疫相关法律法规、食品安全国家标准以及《议定书》规定的情况，中国海关将按照中国相关法律法规予以处置。
+特此公告。
+海关总署
+2025年10月28日
+公告下载链接：
+[海关总署关于进口土耳其扁桃仁检验检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6800372/2025103109125167259.doc)
+[海关总署关于进口土耳其扁桃仁检验检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6800372/2025103109130359456.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6796045/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第204号（关于发布《中华人民共和国海关对海南离岛旅客免税购物监管办法（2025年修订）》的公告）</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕204号 
+【发文机关】海关总署 
+【发布日期】2025-10-25 
+【生效日期】2025-11-01 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第204号（关于发布《中华人民共和国海关对海南离岛旅客免税购物监管办法（2025年修订）》的公告）
+公告〔2025〕204号 
+根据经国务院批准的海南离岛旅客免税购物政策调整事项，以及《中华人民共和国关税法》《中华人民共和国海关进出口货物征税管理办法》，海关总署对《中华人民共和国海关对海南离岛旅客免税购物监管办法》（海关总署2020年第79号公告发布，以下简称《监管办法》）进行了修订，现将修订后的《监管办法》文本及有关内容公告如下：
+一、海关总署对《监管办法》第二条、第三条、第五条、第七条、第十条、第十二条、第十四条、第十七条、第十九条进行了修改。
+二、增加“进入离岛免税商店销售的适用退（免）增值税、消费税政策的国内商品按照本办法监管”的条款。
+修订后的《监管办法》文本详见附件。
+本公告自2025年11月1日起执行，海关总署2020年第79号公告同时废止。
+特此公告。
+附件：[中华人民共和国海关对海南离岛旅客免税购物监管办法.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6796045/2025102814543762529.docx)
+海关总署
+2025年10月25日
+公告正文下载链接：
+[海关总署关于发布《中华人民共和国海关对海南离岛旅客免税购物监管办法（2025年修订）》的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6796045/2025102814544610659.doc)
+[海关总署关于发布《中华人民共和国海关对海南离岛旅客免税购物监管办法（2025年修订）》的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6796045/2025102814545741491.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6800375/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第207号（关于进口阿塞拜疆榛子和扁桃仁检验检疫和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕207号 
+【发文机关】海关总署 
+【发布日期】2025-10-28 
+【生效日期】2025-10-28 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第207号（关于进口阿塞拜疆榛子和扁桃仁检验检疫和卫生要求的公告）
+公告〔2025〕207号 
+根据我国法律法规和中华人民共和国海关总署（以下称中方）与阿塞拜疆共和国食品安全局（以下称阿方）有关阿塞拜疆榛子和扁桃仁输华检验检疫和卫生要求的规定，即日起，允许符合以下要求的阿塞拜疆榛子和扁桃仁进口。
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《中华人民共和国进出口商品检验法》及其实施条例；
+（四）《中华人民共和国进出口食品安全管理办法》；
+（五）《中华人民共和国海关总署与阿塞拜疆共和国食品安全局关于阿塞拜疆榛子和扁桃仁输华检验检疫和卫生要求议定书》（以下简称《议定书》）。
+二、允许进口的产品
+允许进口的榛子和扁桃仁，是指由阿塞拜疆境内种植的欧洲榛（Corylus avellana L）和扁桃树（Prunus dulcis）成熟果实为原料，在阿塞拜疆境内经挑选、干燥、去壳等工艺且未熟制的可供人类食用的坚果。
+三、食品安全要求
+阿塞拜疆输华榛子和扁桃仁应符合中国食品安全和植物检疫法律法规、食品安全国家标准以及《议定书》的规定。
+四、植物检疫要求
+（一）输华榛子不得带有以下中方关注的检疫性有害生物：美国白蛾（Hyphantria cunea）、榛实象（Curculio nucum）。
+（二）输华扁桃仁不得带有以下中方关注的检疫性有害生物：美国白蛾（Hyphantria cunea）、美澳型核果褐腐病菌（Monilinia fructicola）。
+（三）输华榛子和扁桃仁不得带有活虫、虫卵、土壤，不得混有杂草种子、植物残体、金属异物和砂砾等杂质。
+五、企业要求
+阿方应按中方进口食品境外生产企业注册相关要求对阿塞拜疆输华榛子和扁桃仁生产、加工、存放单位进行检查，将符合中方要求的企业向中方推荐。中方对符合要求的企业予以注册。企业获得在华注册后，其产品方可输华。获得注册的阿塞拜疆共和国输华榛子和扁桃仁企业名单可通过海关总署网站查询。
+六、原料要求
+输华榛子和扁桃仁原料应来自经阿方确认符合相关植物检疫和食品安全要求的榛树和扁桃树种植企业。
+七、加工过程要求
+阿方应对输华榛子和扁桃仁的原料种植、生产、加工、贮存、运输、出口等过程进行指导和监管，确保符合中国和阿塞拜疆的相关食品安全和植物卫生要求，防止受到致病微生物或有毒有害物质的污染。
+八、包装、标识要求
+输华榛子和扁桃仁应使用干净、卫生、透气、新的、符合食品安全和植物检疫要求的材料包装，并在运输过程中防止发生撒漏。每一包装应以中文或英文标注“本产品输往中华人民共和国/This product is exported to the People's Republic of China”，以及产品的品名、保质期、产地、生产加工企业及其在华注册编号、出口商名称和地址等可追溯信息。上述信息可以以标签形式粘贴在包装上。
+九、运输要求
+装运前，阿方应对输华榛子和扁桃仁的运输工具进行检查。运输工具应符合卫生要求，不得带有检疫性有害生物或其他限定性检疫物，如杂草籽、活体昆虫、植物残体、土壤以及其他杂质。
+十、证书要求
+出口前，阿方应对经检验检疫符合《议定书》要求的输华榛子和扁桃仁出具植物检疫证书。
+输华榛子植物检疫证书附加声明栏中应注明榛子生产加工企业名称、在华注册编号及“The consignment certified by this phytosanitary certificate complies with the provisions of the Protocol on Inspection, Quarantine and Sanitary Requirements for Hazelnut and Almond Exported from the Republic of Azerbaijan to the People's Republic of China signed by both sides on October 14th, 2025. The consignment is free from Hyphantria cunea, Curculio nucum and other quarantine pests of concern to the People's Republic of China.”（该植物检疫证书所证明的货物符合中阿双方于2025年10月14日签署的关于阿塞拜疆榛子和扁桃仁输华植物检验检疫和卫生要求议定书的规定。该批货物不带有美国白蛾（Hyphantria cunea）、榛实象（Curculio nucum）等中方关注的检疫性有害生物）。
+输华扁桃仁植物检疫证书附加声明栏中应注明扁桃仁生产加工企业名称、在华注册编号及“The consignment certified by this phytosanitary certificate complies with the provisions of the Protocol on Inspection, Quarantine and Sanitary Requirements for Hazelnut and Almond Exported from the Republic of Azerbaijan to the People's Republic of China signed by both sides on October 14th, 2025. The consignment is free from Hyphantria cunea, Monilinia fructicola and other quarantine pests of concern to the People's Republic of China.”（该植物检疫证书所证明的货物符合中阿双方于2025年10月14日签署的关于阿塞拜疆榛子和扁桃仁输华植物检验检疫和卫生要求议定书的规定。该批货物不带有美国白蛾（Hyphantria cunea）、美澳型核果褐腐病菌（Monilinia fructicola）等中方关注的检疫性有害生物）。
+十一、进境检验检疫及不合格处理
+（一）进境检验检疫。输华榛子和扁桃仁到达中国入境口岸后，中国海关将实施检验检疫监管，合格后准予进境。
+（二）不合格处理。中方在输华榛子和扁桃仁中如发现存在违反中国食品安全和植物检疫相关法律法规、食品安全国家标准以及《议定书》规定的情况，中方将按照中国相关法律法规予以处置。
+特此公告。
+海关总署
+2025年10月28日
+公告下载链接：
+[海关总署关于进口阿塞拜疆榛子和扁桃仁检验检疫和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6800407/2025103109273581916.doc)
+[海关总署关于进口阿塞拜疆榛子和扁桃仁检验检疫和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6800407/2025103109274617979.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6800407/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第210号（关于增列、调整、废止监管方式代码的公告）</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕210号 
+【发文机关】海关总署 
+【发布日期】2025-10-31 
+【生效日期】2025-10-31 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第210号（关于增列、调整、废止监管方式代码的公告）
+公告〔2025〕210号 
+为规范和便利免税店销售国内商品以及特定人员进境自用车辆监管和通关，决定增列海关监管方式代码“1775”，调整海关监管方式代码“2439”、“9739”和废止海关监管方式代码“1831”，现将有关事项公告如下：
+一、增列监管方式代码“1775”，全称“免税店销售国内商品”，适用于具有免税商品经营资质的企业、经国务院批准允许参与免税商店经营的外商投资企业和具有离岛免税品经销资格的企业，统一采购专供其所属经批准可适用国内商品退（免）增值税、消费税政策的免税商店销售的国内商品。
+二、将监管方式代码“2439”全称调整为“外国常驻机构进出境公用物品及个人进境自用车辆”，简称调整为“常驻机构公用及个人自用车辆”，适用范围调整为“1．常驻机构进境自用且数量合理的办公用机器设备、家具、文具、机动车辆等及复运出境的原进境的公用物品。2．外商投资企业外方常驻人员和外国驻华机构的常驻人员，持有长期居留证件和来华定居的引进专家，以及离任回国的我国驻外使领馆人员等进境自用车辆”。
+三、删除监管方式代码“9739”适用范围中“外商投资企业外方常驻人员和外国驻华机构的常驻人员，以及持有长期居留证件和来华定居的引进专家等进口自用汽车。”
+四、外汇商品免税店的相关政策已经取消，为规范海关管理和贸易统计，废止海关监管方式代码“1831”，全称“免税外汇商品”，简称“外汇商品”。免税外汇商品是指由经批准的经营单位进口，销售专供入境的我国特定出国人员和驻华外交人员的免税外汇商品。
+上述规定自发布之日起施行。
+特此公告。
+海关总署
+2025年10月31日
+公告下载链接：
+[海关总署关于增列、调整、废止监管方式代码的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6804213/2025110312404268180.doc)
+[海关总署关于增列、调整、废止监管方式代码的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6804213/2025110312405137919.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6804213/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>海关总署 农业农村部公告2025年第208号（关于防止厄立特里亚口蹄疫传入我国的公告）</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕208号 
+【发文机关】海关总署 农业农村部 
+【发布日期】2025-10-29 
+【生效日期】2025-10-29 
+【效力】有效 
+【效力说明】
+## 海关总署 农业农村部公告2025年第208号（关于防止厄立特里亚口蹄疫传入我国的公告）
+公告〔2025〕208号 
+2025年9月17日，厄立特里亚向世界动物卫生组织报告，该国安塞巴省（Anseba）发生口蹄疫。为防止疫情传入，保护我国畜牧业安全和生物安全，根据相关法律法规，现公告如下：
+一、禁止直接或间接从厄立特里亚输入偶蹄动物及其相关产品（源于偶蹄动物未经加工或者虽经加工但仍有可能传播疫病的产品）。
+二、禁止寄递或携带来自厄立特里亚的偶蹄动物及其相关产品入境。一经发现一律作退回或销毁处理。
+三、来自厄立特里亚的进境运输工具上卸下的动植物性废弃物、泔水等，一律在海关的监督下作除害处理，不得擅自抛弃。
+四、对边防检查等部门截获的非法入境的来自厄立特里亚的偶蹄动物及其相关产品，一律在海关的监督下作销毁处理。
+五、凡违反上述规定者，由海关依照《中华人民共和国海关法》、《中华人民共和国生物安全法》、《中华人民共和国进出境动植物检疫法》及其实施条例有关规定处理。
+六、各级海关、各级农业农村部门要分别按照《中华人民共和国海关法》《中华人民共和国生物安全法》《中华人民共和国进出境动植物检疫法》《中华人民共和国动物防疫法》等有关规定，密切配合，做好检疫、防疫和监督工作。
+本公告自发布之日起实施。
+特此公告。
+海关总署 农业农村部
+2025年10月29日
+公告下载链接：
+[海关总署 农业农村部关于防止厄立特里亚口蹄疫传入我国的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6809986/2025110608371013619.doc)
+[海关总署 农业农村部关于防止厄立特里亚口蹄疫传入我国的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6809986/2025110608371947417.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6809986/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>海关总署 农业农村部公告2025年第209号（关于防止马里牛传染性胸膜肺炎传入我国的公告）</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕209号 
+【发文机关】海关总署 农业农村部 
+【发布日期】2025-10-29 
+【生效日期】2025-10-29 
+【效力】有效 
+【效力说明】
+## 海关总署 农业农村部公告2025年第209号（关于防止马里牛传染性胸膜肺炎传入我国的公告）
+公告〔2025〕209号 
+近日，马里向世界动物卫生组织报告，该国发生牛传染性胸膜肺炎。为防止疫情传入，保护我国畜牧业安全和生物安全，根据相关法律法规，现公告如下：
+一、禁止直接或间接从马里输入牛及其相关产品（源于牛未经加工或者虽经加工但仍有可能传播疫病的产品）。
+二、禁止寄递或携带来自马里的牛及其相关产品入境。一经发现一律作退回或销毁处理。
+三、来自马里的进境运输工具上卸下的动植物性废弃物、泔水等，一律在海关的监督下作除害处理，不得擅自抛弃。
+四、对边防检查等部门截获的非法入境的来自马里的牛及其相关产品，一律在海关的监督下作销毁处理。
+五、凡违反上述规定者，由海关依照《中华人民共和国海关法》、《中华人民共和国生物安全法》、《中华人民共和国进出境动植物检疫法》及其实施条例有关规定处理。
+六、各级海关、各级农业农村部门要分别按照《中华人民共和国海关法》《中华人民共和国生物安全法》《中华人民共和国进出境动植物检疫法》《中华人民共和国动物防疫法》等有关规定，密切配合，做好检疫、防疫和监督工作。
+本公告自发布之日起实施。
+特此公告。
+海关总署 农业农村部
+2025年10月29日
+公告下载链接：
+[海关总署 农业农村部关于防止马里牛传染性胸膜肺炎传入我国的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6809990/2025110608385332350.doc)
+[海关总署 农业农村部关于防止马里牛传染性胸膜肺炎传入我国的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6809990/2025110608390290630.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6809990/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>海关总署 农业农村部公告2025年第212号（关于防止日本蓝舌病传入我国的公告）</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕212号 
+【发文机关】海关总署 农业农村部 
+【发布日期】2025-10-31 
+【生效日期】2025-10-31 
+【效力】有效 
+【效力说明】
+## 海关总署 农业农村部公告2025年第212号（关于防止日本蓝舌病传入我国的公告）
+公告〔2025〕212号 
+近日，日本向世界动物卫生组织报告发生蓝舌病。为防止疫情传入，保护我国畜牧业安全和生物安全，根据相关法律法规，现公告如下：
+一、禁止直接或间接从日本输入反刍动物及相关产品（源于反刍动物未经加工或者虽经加工但仍有可能传播疫病的产品）。
+二、禁止寄递或携带来自日本的反刍动物及相关产品入境。一经发现一律作退回或销毁处理。
+三、来自日本的进境航空器、船舶、铁路列车等运输工具上卸下的动植物性废弃物、泔水等，一律在海关的监督下作除害处理，不得擅自抛弃。
+四、对边防检查等部门截获的非法入境的来自日本的反刍动物及相关产品，一律在海关的监督下作销毁处理。
+五、凡违反上述规定者，由海关依照《中华人民共和国海关法》、《中华人民共和国生物安全法》、《中华人民共和国进出境动植物检疫法》及其实施条例有关规定处理。
+六、各级海关、各级农业农村部门要分别按照《中华人民共和国海关法》《中华人民共和国生物安全法》《中华人民共和国进出境动植物检疫法》《中华人民共和国动物防疫法》等有关规定，密切配合，做好检疫、防疫和监督工作。
+本公告自发布之日起实施。
+特此公告。
+海关总署 农业农村部
+2025年10月31日
+公告下载链接：
+[海关总署 农业农村部关于防止日本蓝舌病传入我国的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6809994/2025110608404274379.doc)
+[海关总署 农业农村部关于防止日本蓝舌病传入我国的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6809994/2025110608405036293.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6809994/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>海关总署 农业农村部公告2025年第215号（关于解除巴西高致病性禽流感疫情禁令的公告）</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕215号 
+【发文机关】海关总署 农业农村部 
+【发布日期】2025-10-31 
+【生效日期】2025-10-31 
+【效力】有效 
+【效力说明】
+## 海关总署 农业农村部公告2025年第215号（关于解除巴西高致病性禽流感疫情禁令的公告）
+公告〔2025〕215号 
+根据风险分析结果，自本公告发布之日起，解除巴西高致病性禽流感疫情禁令。
+海关总署、农业农村部2025年联合公告第107号同时废止。
+特此公告。
+海关总署 农业农村部
+2025年10月31日
+公告下载链接：
+[海关总署 农业农村部关于解除巴西高致病性禽流感疫情禁令的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6814587/2025111011011434370.doc)
+[海关总署 农业农村部关于解除巴西高致病性禽流感疫情禁令的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6814587/2025111011012462299.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6814587/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第213号（关于进口保加利亚野生水产品检验和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕213号 
+【发文机关】海关总署 
+【发布日期】2025-11-06 
+【生效日期】2025-11-06 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第213号（关于进口保加利亚野生水产品检验和卫生要求的公告）
+公告〔2025〕213号 
+根据我国法律法规，中华人民共和国海关总署（以下称中方）与保加利亚共和国农业和食品部（以下称保方）有关保加利亚输华野生水产品的检验和卫生要求规定，即日起，允许符合以下相关要求的保加利亚野生水产品进口：
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
+（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
+（三）《中华人民共和国海关总署与保加利亚共和国农业和食品部关于保加利亚输华野生水产品的检验和卫生要求议定书》（以下简称《议定书》）。
+二、进口产品范围
+野生水产品，是指野生的、供人类食用的水生动物产品及其制品、藻类等海洋植物产品及其制品，不包括活水生动物及水生动植物繁殖材料。
+三、生产企业要求
+向中国出口野生水产品的生产企业（包括生产、加工、贮存企业），应获保加利亚官方批准并受其有效监督。生产企业的食品安全卫生管理和防护体系应当符合中国食品安全相关法律法规的要求。
+向中国出口野生水产品的生产企业应当由保方向中方推荐注册。未经注册，不得向中国出口。
+四、进口产品要求
+保方应确保输华野生水产品符合以下条件：
+（一）在本国或国际水域合法捕捞。
+（二）原料及产品均不存在以下所涉及的情况：
+1．保加利亚已输华或拟输华野生水产品严重违反中国食品安全相关法律法规以及《议定书》规定。
+2．保加利亚境内发生《中华人民共和国进境动物检疫疫病名录》（以下简称《名录》）中列明的和世界动物卫生组织（WOAH）规定的必须通报的与《议定书》产品相关的水生动物疫病，已经严重影响输华野生水产品安全。
+3．保加利亚境内发生重大食品安全事件，或生产企业发生重大公共卫生事件，或捕捞水域受到污染物影响，已经严重影响输华野生水产品安全。
+（三）未直接或间接使用中国禁用的药物或添加剂，按规定使用中方限用或允许使用的药物或添加剂。
+（四）经主管部门检验检疫，未发现中国法律法规中列明的致病微生物、有毒有害物质和异物，以及任何传染病和寄生虫病的病例，未发现《名录》中列明的和WOAH规定的必须通报的水生动物疫病。
+（五）生产过程（包括捕捞、生产加工、包装、储存、运输、中转和出口等）均应符合中国相关安全卫生要求和可追溯要求。
+（六）产品的包装、标签标识应当符合中国食品安全国家标准和进口食品安全管理相关规定。
+五、证书要求
+保方负责按照中方的要求，对输华野生水产品实施检验检疫，并对向中国出口的每批野生水产品出具经双方确认的卫生证书，证明该批产品符合中国食品安全相关法律法规的有关规定。证书至少用中文、英文印制（填写证书时英文为必选语言）。
+卫生证书应完整填写输华野生水产品生产企业的信息。保方应及时将证书样本和官方印章提供中方备案。如有变更，保方应至少在生效前一个月向中方备案。
+六、其他要求
+中国海关将依照中国法律法规、标准和《议定书》对输华野生水产品实施检验检疫。
+对于不合格产品，实施销毁、退运或其他处理。对发生严重问题或多次发生不合格问题的生产企业，中方可采取加强检验检疫或暂停进口等措施。
+特此公告。
+海关总署
+2025年11月6日
+公告下载链接：
+[海关总署关于进口保加利亚野生水产品检验和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6814595/2025111011055258848.doc)
+[海关总署关于进口保加利亚野生水产品检验和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6814595/2025111011060254369.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6814595/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第214号（关于进口也门野生水产品检验和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕214号 
+【发文机关】海关总署 
+【发布日期】2025-11-06 
+【生效日期】2025-11-06 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第214号（关于进口也门野生水产品检验和卫生要求的公告）
+公告〔2025〕214号 
+根据我国法律法规和中华人民共和国海关总署（以下称中方）与也门共和国农业、灌溉和渔业部（以下称也方）有关也门输华野生水产品的检验和卫生要求规定，即日起，允许符合以下相关要求的也门野生水产品进口：
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
+（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
+（三）《中华人民共和国海关总署与也门共和国农业、灌溉和渔业部关于也门输华野生水产品的检验和卫生要求议定书》（以下简称《议定书》）。
+二、进口产品范围
+野生水产品，是指野生的、供人类食用的水生动物产品及其制品、藻类等海洋植物产品及其制品，不包括两栖类、爬行类、水生哺乳动物类、《濒危野生动植物种国际贸易公约》（CITES）附录和中国国家重点保护野生动物名录所列物种、活水生动物及水生动植物繁殖材料。
+三、生产企业要求
+向中国出口野生水产品的生产企业（包括生产、加工、贮存企业），应获得也门官方批准并受其有效监督。生产企业的食品安全卫生管理和防护体系应当符合中国食品安全相关法律法规的要求。
+向中国出口野生水产品的生产企业应当由也方向中方推荐注册。未经注册，不得向中国出口。
+四、进口产品要求
+也方应确保输华野生水产品符合以下条件：
+（一）在本国或国际水域合法捕捞。
+（二）原料及产品均未发生以下所列问题：
+1．也门已输华或拟输华野生水产品严重违反中国食品安全相关法律法规以及《议定书》规定。
+2．也门境内发生《中华人民共和国进境动物检疫疫病名录》（以下简称《名录》）中列明的和世界动物卫生组织（WOAH）规定的必须通报的与《议定书》产品相关的水生动物疫病，已经严重影响输华野生水产品安全。
+3．也门境内发生重大食品安全事件，或生产企业发生重大公共卫生事件，或捕捞水域受到污染物影响，已经严重影响输华野生水产品安全。
+（三）未直接或间接使用中国禁用的药物或添加剂，按规定使用中国限用或允许使用的药物或添加剂。
+（四）经主管部门检验检疫，未发现中国法律法规中列明的致病微生物、有毒有害物质和异物，以及任何传染病和寄生虫病的病例，未发现《名录》中列明的和WOAH规定的必须通报的水生动物疫病。
+（五）生产过程（包括捕捞、生产加工、包装、贮存、运输、中转和出口等）均应符合中国相关安全卫生要求和可追溯要求。
+（六）产品的包装、标签标识应当符合中国食品安全国家标准和进口食品安全管理相关规定。
+五、证书要求
+也方负责按照中方的要求，对输华野生水产品实施检验检疫，并对向中国出口的每批野生水产品出具经双方确认的卫生证书，证明该批产品符合中国食品安全相关法律法规的有关规定。证书至少用中文、英文印制（填写证书时英文为必选语言）。
+卫生证书应完整填写输华野生水产品生产企业的信息。也方应及时将证书样本和官方印章提供中方备案。如有变更，也方应至少在生效前一个月向中方备案。
+六、其他要求
+中国海关对输华野生水产品实施检验检疫。
+对于不合格产品，将依照中国法律法规实施销毁、退运或其他处理。对发生严重问题或多次发生不合格问题的生产企业，中方可采取加强检验检疫或暂停进口等措施。
+特此公告。
+海关总署
+2025年11月6日
+公告下载链接：
+[海关总署关于进口也门野生水产品检验和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6814602/2025111011082140812.doc)
+[海关总署关于进口也门野生水产品检验和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6814602/2025111011083265827.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6814602/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第218号（关于废止海关总署2025年第180号公告的公告）</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕218号 
+【发文机关】海关总署 
+【发布日期】2025-11-07 
+【生效日期】2025-11-10 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第218号（关于废止海关总署2025年第180号公告的公告）
+公告〔2025〕218号 
+根据商务部公告2025年第71号，自2025年11月10日起，停止将原产于美国的进口非色散位移单模光纤的现行反倾销税税率适用于原产于美国的进口相关截止波长位移单模光纤。海关总署决定相应废止海关总署2025年第180号公告（海关总署关于相关截止波长位移单模光纤商品编号申报要求的公告）。
+自2025年11月10日起，进口货物收货人或者其代理人在申报进口原产于美国的相关截止波长位移单模光纤（税则号列90011000）时，商品编号应填报90011000.90。
+本公告自2025年11月10日起施行。
+特此公告。
+海关总署
+2025年11月7日
+公告下载链接：
+[海关总署关于废止海关总署2025年第180号公告的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6814659/2025111011162267786.doc)
+[海关总署关于废止海关总署2025年第180号公告的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6814659/2025111011163176816.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6814651/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第217号（关于废止海关总署2025年第30号公告的公告）</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕217号 
+【发文机关】海关总署 
+【发布日期】2025-11-07 
+【生效日期】2025-11-10 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第217号（关于废止海关总署2025年第30号公告的公告）
+公告〔2025〕217号 
+基于对美方整改措施的评估结果，依据我国相关法律法规和国际植物检疫措施标准，海关总署决定废止海关总署2025年第30号公告（关于暂停美国CHS Inc.等3家企业大豆输华资质的公告），自2025年11月10日起恢复CHS Inc.等3家企业大豆输华资质。
+特此公告。
+海关总署
+2025年11月7日
+公告下载链接：
+[海关总署关于废止海关总署2025年第30号公告的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6814651/2025111011132073344.doc)
+[海关总署关于废止海关总署2025年第30号公告的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6814651/2025111011132838732.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6814659/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第216号（关于废止海关总署2025年第29号公告的公告）</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕216号 
+【发文机关】海关总署 
+【发布日期】2025-11-07 
+【生效日期】2025-11-10 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第216号（关于废止海关总署2025年第29号公告的公告）
+公告〔2025〕216号 
+基于对美方整改措施的评估结果，依据我国相关法律法规和国际植物检疫措施标准，海关总署决定废止海关总署2025年第29号公告（关于暂停进口美国原木的公告）。本公告自2025年11月10日起施行。
+特此公告。
+海关总署
+2025年11月7日
+公告下载链接：
+[海关总署关于废止海关总署2025年第29号公告的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6814670/2025111011113864203.doc)
+[海关总署关于废止海关总署2025年第29号公告的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6814670/2025111011114713818.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6814670/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第219号（关于进境农产品境外企业申报管理有关要求的公告）</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕219号 
+【发文机关】海关总署 
+【发布日期】2025-11-07 
+【生效日期】2025-12-15 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第219号（关于进境农产品境外企业申报管理有关要求的公告）
+公告〔2025〕219号 
+为进一步强化进境农产品溯源管理，提高通关效率，根据《中华人民共和国进出境动植物检疫法》及其实施条例等有关规定，现就进境农产品境外企业申报管理有关要求公告如下：
+一、根据国际植物检疫措施标准，海关总署对进境农产品的检疫风险开展分析，结合国际惯例确定需境外官方推荐注册登记的进境农产品目录（以下简称目录）并对外公布，查询地址为http://dzs.customs.gov.cn/dzs/2747042/6787828/index.html。进口商应确保进口目录内的农产品来自海关公布的注册状态正常的境外企业。
+二、经注册登记的境外企业可通过“进境动植物及其产品境外企业检疫注册登记名单”进行查询，查询地址为http://dzs.customs.gov.cn/dzs/2747042/6787828/index.html，或可通过“互联网+海关”平台“我要查”栏目“动植检信息查询”功能查询，查询地址为https://online.customs.gov.cn/ociswebserver/pages/dzjxxcx/index.html。
+三、进口商申报目录内的农产品进口时，应在报关单或备案清单的“产品资质”项下“进境动植物及其产品境外生产、加工、存放企业注册登记”证书栏（许可证类别代码302）规范填写境外企业的中方注册号（在华注册编号）。同一报关单涉及多个商品项的，应逐项填写对应企业的中方注册号（在华注册编号）。
+本公告自2025年12月15日实施。
+特此公告。
+海关总署
+2025年11月7日
+公告下载链接：
+[海关总署关于进境农产品境外企业申报管理有关要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6818144/2025111208194739437.doc)
+[海关总署关于进境农产品境外企业申报管理有关要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6818144/2025111208200044790.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6818144/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第223号（关于进口伊朗猕猴桃检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕223号 
+【发文机关】海关总署 
+【发布日期】2025-11-18 
+【生效日期】2025-11-18 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第223号（关于进口伊朗猕猴桃检疫要求的公告）
+公告〔2025〕223号 
+根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与伊朗伊斯兰共和国农业部（以下称伊方）有关伊朗鲜食猕猴桃输华植物检疫要求的规定，即日起，允许符合以下相关要求的伊朗鲜食猕猴桃进口。
+一、检验检疫依据
+（一）《中华人民共和国生物安全法》；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《中华人民共和国食品安全法》及其实施条例；
+（四）《进境水果检验检疫监督管理办法》；
+（五）《中华人民共和国海关总署与伊朗伊斯兰共和国农业部关于伊朗鲜食猕猴桃输华植物检疫要求议定书》。
+二、允许进境商品名称
+鲜食猕猴桃（以下简称猕猴桃），学名Actinidia deliciosa，英文名 Kiwi Fruits。
+三、允许的产地
+伊朗猕猴桃产区。
+四、批准的果园和包装厂
+输华猕猴桃的果园、包装厂及冷处理设施须经伊方审核，并由中方批准注册。注册信息包括名称、地址及注册号码，以便在出口货物不符合本公告规定时准确溯源。每年出口季前，由伊方向中方提供企业名单，经中方审核批准后在海关总署网站上公布。
+五、中方关注的检疫性有害生物名单
+1．地中海实蝇Ceratitis capitata
+2．葡萄花翅小卷蛾Lobesia botrana
+3．无花果蜡蚧Ceroplastes rusci
+4．丁香假单胞菌猕猴桃致病变种Pseudomonas syringae pv. actinidiae
+5．绿黄假单胞菌Pseudomonas viridiflava
+六、出口前管理
+（一）果园管理。
+1．输华猕猴桃果园应在伊方监管下建立完善的质量管理和溯源体系，实施良好农业操作规范（GAP）或进行植物检疫管理，维持果园卫生条件，及时清理落果、收获时剔除烂果等，并实施有害生物综合治理（IPM），包括定期开展有害生物监测调查，物理、化学或生物防治有害生物，以及农事操作等控制措施，以控制可能发生的有害生物。
+2．伊方应按国际植物检疫措施标准第6号（ISPM 6）的要求，针对中方关注的检疫性有害生物制定管理计划，组织实施果园监测。在贸易开始的第一年，监测方案和相应的综合防治措施须由伊方监督进行，并应要求向中方提供详细措施。果园有害生物监测与防治应在技术人员监管和指导下实施，技术人员应接受伊方或其授权机构的培训。一旦发现中方关注的检疫性有害生物，应立即采取防治和控制措施。
+3．所有输华果园应保留有害生物的监测和防治记录，并应要求向中方提供。防治记录包括在生长季节内使用的所有化学药剂的名称、活性成分、施用日期、药剂浓度及使用量等详细信息。
+4．针对地中海实蝇，输华果园须取田间综合管理措施，包括开展监测诱捕，使用化学防治或生物防治等方法，以降低地中海实蝇种群密度。监测时间应从开花期开始至采收期结束。输华果园内诱捕器设置的密度为每公顷1个（不足3公顷的果园至少设置3个诱捕器），每2周检查一次诱捕器。一旦监测到地中海实蝇，应立即进行有效防治。
+5．针对葡萄花翅小卷蛾，输华果园须采取田间综合管理措施，包括开展监测诱捕，使用化学防治或生物防治等方法，以降低葡萄花翅小卷蛾的密度。监测时间应从开花期开始至采收期结束，输华果园内诱捕器设置的密度为每公顷设置1个（不足3公顷的果园至少设置3个诱捕器），每2周检查一次诱捕器，每四周更换一次诱芯。一旦监测到葡萄花翅小卷蛾，应立即进行有效防治。
+6．针对无花果蜡蚧，输华果园应在伊方技术人员监管和指导下开展监测，从开花至收获期，重点调查枝干、茎、叶和果实是否有无花果蜡蚧。如发现该有害生物症状，应立即采取措施，如生物、物理或化学方法防治，控制有害生物的发生。
+7．针对丁香假单胞菌猕猴桃致病变种和绿黄假单胞菌，输华果园应在伊方指导下开展监测。监测从开花期至收获期，至少每2周调查一次。如在监测中发现有害生物或其相应症状，应采用生物、物理或化学方法及时防治。防治不彻底的果园，伊方将暂停该果园输华资格，并立即通知中方。应要求，伊方应向中方提供关于这两种有害生物的调查报告或管理记录。
+（二）包装厂管理。
+1．输华猕猴桃的加工、包装、储藏和装运过程，应在伊方或其授权官员检疫监管下进行。包装和冷藏设施应保持良好的卫生状态，并应具备防止有害生物再感染的功能（如防虫网）。
+2．在包装过程中，猕猴桃须经水洗、刷果、杀菌、挑拣、分级，剔除有缺陷的果实，以保证不带有昆虫、螨类、烂果及枝、叶和土壤。
+3．包装好的猕猴桃如需存储，应当立即入库并单独存放，避免受到有害生物再次感染。
+4．装运输华猕猴桃的集装箱必须在装箱时检查以确保其具备良好的卫生条件。
+（三）包装要求。
+1．包装材料应干净卫生、未使用过，符合中国有关植物检疫和卫生要求。如使用木质包装，须符合国际植物检疫措施标准第15号（ISPM 15）要求。
+2．每个包装箱上须应用中文或英文注明水果名称、国家、产地、果园和包装厂的名称或其注册号码等信息。每个包装箱和托盘应用中文或英文标出“输往中华人民共和国”或“Exported to the People’s Republic of China”。
+（四）检疫处理要求。
+输华猕猴桃应针对地中海实蝇采取冷处理措施，冷处理应在伊方或其授权人员的监管下，按照出口前冷处理操作程序（附件1）或出口运输途中冷处理操作程序（附件2）进行。冷处理指标要求应满足以下任一条件：
+（1）1.11°C或以下（果肉温度），连续处理14天或以上；
+（2）1.67°C或以下（果肉温度），连续处理16天或以上；
+（3）2.22°C或以下（果肉温度），连续处理18天或以上。
+（五）出口前检验检疫。
+1．伊方或其授权机构应按照每批货物2%的比例对输华猕猴桃进行抽样检查。最小取样量为1200个果实，同时至少对其中的60个果实或检查过程中发现的可疑果实进行剖果检查或检疫鉴定。如两年内没有发生植物检疫问题，抽样比例数可降为1%，但不得少于600个果实。
+2．如发现中方关注的检疫性有害生物、枝叶或土壤，整批货物不得出口中国，相关果园、包装厂在本出口季不得向中国出口，直至伊方查明原因，并采取改进措施。同时，伊方应保存查获记录，应要求提供给中方。
+（六）植物检疫证书要求。
+1．经检疫合格的货物，伊方应按国际植物检疫措施标准第12号（ISPM 12）出具植物检疫证书，注明果园和包装厂名称或注册号码，并填写以下附加声明：“This consignment complies with requirements specified in the Protocol of Phytosanitary Requirements for Export of Fresh Kiwi Fruits from Iran to China, and is free from any quarantine pests of concern to China.”（该批货物符合伊朗鲜食猕猴桃输华植物检疫议定书要求，不带中方关注的检疫性有害生物。）
+2．对于实施出口前检疫处理的，应在植物检疫证书上注明检疫处理方式，处理温度、持续时间及处理设施名称或注册号码等信息。对于实施运输途中冷处理的，应在植物检疫证书上标注“Cold treatment in transit”（途中冷处理），并注明处理温度、持续时间、集装箱号码及封识号码等。
+3． 贸易正式开始前，伊方应向中方提供植物检疫证书样本。
+七、进境检验检疫及不合格处理
+输华猕猴桃到达中国进境口岸时，中国海关按照以下要求实施检验检疫。
+（一）有关证书和标识核查。
+1．核查进口猕猴桃是否获得进境动植物检疫许可证。
+2．核查植物检疫证书是否符合本公告第六条第（六）项的规定。
+3．核查包装箱和托盘上的标识是否符合本公告第六条第（三）项的规定。
+4．对于出口前实施冷处理的货物，需核查植物检疫证书、伊方签字确认的冷处理结果报告单以及果温探针校正记录等是否满足本公告第六条第（四）项的规定。
+5．对于运输途中实施冷处理的货物，需核查植物检疫证书、冷处理报告、果温探针校正记录等是否满足本公告第六条第（四）项的规定。
+（二）进境检验检疫。
+1．输华猕猴桃应从中方允许进口水果的口岸进境。
+2．根据有关法律、行政法规、规章等规定及本公告要求对进口猕猴桃实施检验检疫，经检验检疫合格的，准予进境。
+（三）不合格处理。
+1．如发现来自未经批准果园、包装厂或冷处理设施，则该批货物禁止进境。
+2．如冷处理被认定无效，则该批货物将被采取到岸冷处理（可在本集装箱内进行）、退回、销毁等处理措施。
+3．如发现中方关注的检疫性有害生物或伊朗新发生的检疫性有害生物活体，或发现土壤、植物残体等，则该批货物作退回、销毁或检疫除害处理。
+4．如发现不符合中国食品安全法律法规和国家标准的，该批货物作退回或销毁处理。
+特此公告。
+附件：
+[1.出口前冷处理操作程序.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6837376/2025112015595910506.docx)
+[2.运输途中冷处理操作程序.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6837376/2025112016000733786.docx)
+海关总署
+2025年11月18日
+公告正文下载链接：
+[海关总署关于进口伊朗猕猴桃检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6837376/2025112016001670566.doc)
+[海关总署关于进口伊朗猕猴桃检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6837376/2025112016002730956.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6822872/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第220号（关于进口乌兹别克斯坦养殖水产品检验检疫和兽医卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕220号 
+【发文机关】海关总署 
+【发布日期】2025-11-12 
+【生效日期】2025-11-12 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第220号（关于进口乌兹别克斯坦养殖水产品检验检疫和兽医卫生要求的公告）
+公告〔2025〕220号 
+根据我国法律法规和中华人民共和国海关总署（以下称中方）与乌兹别克斯坦共和国农业部（以下称乌方）有关乌兹别克斯坦输华养殖水产品的检验检疫和兽医卫生要求规定，即日起，允许符合以下相关要求的乌兹别克斯坦养殖水产品进口：
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
+（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
+（三）《中华人民共和国海关总署与乌兹别克斯坦共和国农业部关于乌兹别克斯坦共和国输华养殖水产品的检验检疫和兽医卫生要求议定书》（以下简称《议定书》）。
+二、进口产品范围
+养殖水产品，是指人工养殖的、供人类食用的水生动物产品及其制品、藻类等水生植物产品及其制品，不包括《濒危野生动植物种国际贸易公约》（CITES）附录和中国国家重点保护野生动物名录所列物种、活水生动物及水生动植物繁殖材料。乌兹别克斯坦输华养殖水产品目录见附件。
+三、生产企业要求
+向中国出口养殖水产品的生产企业（包括加工、贮存企业）和养殖场，应获乌兹别克斯坦官方批准并受其有效监督。生产企业的食品安全卫生条件应当符合中国和乌兹别克斯坦有关食品安全法律法规的要求。
+向中国出口养殖水产品的生产企业应当由乌方向中方推荐注册，未经注册，不得向中国出口。
+四、进口产品要求
+乌方应确保输华养殖水产品符合以下条件：
+（一）在本国水域养殖。
+（二）原料及产品均未发生以下所列问题：
+1．乌兹别克斯坦境内发生《中华人民共和国进境动物检疫疫病名录》（以下简称《疫病名录》）中列明的和世界动物卫生组织（WOAH）规定的必须通报的与本公告产品相关的水生动物疫病，使输华养殖水产品受到或可能受到感染；
+2．乌兹别克斯坦境内发生任何重大食品安全事件，已经影响或可能影响输华养殖水产品安全；
+3．乌方已输华或拟输华养殖水产品严重违反中国和乌兹别克斯坦法律法规规定以及《议定书》规定；
+4．生产企业发生重大公共卫生事件，如员工感染重大传染病，已经污染或可能污染输华养殖水产品及其包装、运输工具；
+5．养殖区域受到污染物影响，已经污染或可能污染输华养殖水产品。
+（三）未直接或间接（如在饲料中添加）使用双方禁用的药物或添加剂，按规定使用双方允许使用的药物或添加剂；经主管当局检验，未发现中国和乌兹别克斯坦法律法规规定中列明的致病微生物、有毒有害物质和异物。
+（四）所有输华养殖水产品经主管当局检验检疫，是安全的，适合人类食用，未发现任何传染病和寄生虫病的病理指征，未发现《疫病名录》中列明的和WOAH规定的必须通报的水生动物疫病。
+（五）养殖、生产加工、包装、存储、运输、中转和出口等全过程均符合双方相关水产品安全卫生要求和可追溯要求。
+五、证书要求
+向中国出口的每批或每一集装箱养殖水产品应至少随附一份正本兽医卫生证书，证明该批产品符合中国和乌兹别克斯坦食品安全相关法律法规及《议定书》的有关规定。乌方应在兽医卫生证书上完整填写从养殖、生产加工、包装、储存、运输、中转和出口等全过程中涉及的生产企业信息，包括养殖场、生产企业名称及注册号。
+证书应用英文、中文、乌兹别克文印制（填写证书时英文为必选语言）。证书的格式、内容须事先获得双方认可。乌方应及时将证书样本、官方签发机构印章和签字官员笔迹提供给中方备案。如证书样本的内容和格式、官方签发机构印章和签字官员笔迹有变更，乌方应至少在生效前一个月向中方备案。
+六、包装和标识要求
+输华养殖水产品应有外包装和单独的内包装。内外包装应是符合国际食品安全标准的全新材料，满足防止外界因素污染的要求。
+内外包装应当有中英文标识，标明以下内容：商品名和学名、规格、生产日期、批号、保质期限和保存条件、生产方式（养殖）、生产地区（养殖产品所在国家或者地区）、生产企业（含独立冷库）名称、注册编号及地址（具体到州/省/市）、目的地（必须标注为中华人民共和国）。
+以预包装形式输华的水产品，预包装的中文标签应符合中国预包装食品标签要求。
+七、其他要求
+中国海关将依照中国法律法规规定对进口养殖水产品实施检验检疫。
+对于不合格产品，实施退回、销毁或其他处理。对发生严重问题或多次发生不合格问题的生产企业，中方将采取加强检验检疫或暂停进口等措施。
+特此公告。
+附件：[乌兹别克斯坦共和国输华养殖水产品目录.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6822872/2025111408433161265.doc)
+海关总署
+2025年11月12日
+公告正文下载链接：
+[海关总署关于进口乌兹别克斯坦养殖水产品检验检疫和兽医卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6822872/2025111408434064855.doc)
+[海关总署关于进口乌兹别克斯坦养殖水产品检验检疫和兽医卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6822872/2025111408434965758.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6823152/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第221号（关于进口冰岛野生水产品检验和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕221号 
+【发文机关】海关总署 
+【发布日期】2025-11-13 
+【生效日期】2025-11-13 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第221号（关于进口冰岛野生水产品检验和卫生要求的公告）
+公告〔2025〕221号 
+根据我国法律法规和中华人民共和国海关总署（以下称中方）与冰岛共和国产业部（以下称冰方）有关冰岛输华野生水产品的检验和卫生要求规定，即日起，允许符合以下相关要求的冰岛野生水产品进口：
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
+（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
+（三）《中华人民共和国海关总署与冰岛共和国产业部关于冰岛输华野生水产品的检验和卫生要求议定书》（以下简称《议定书》）。
+二、进口产品范围
+野生水产品，是指野生捕捞或获得的、供人类食用的水生动物产品及其制品、水生藻类产品及其制品，不包括两栖类、爬行类、水生哺乳动物类、《濒危野生动植物种国际贸易公约》（CITES）附录和中国国家重点保护野生动物名录所列物种、活水生动物及水生动植物繁殖材料。
+三、生产企业要求
+向中国出口野生水产品的生产企业（包括生产、加工、贮存企业），应获冰岛官方批准并受其监督。生产企业符合中国和冰岛的兽医卫生和公共卫生要求。
+向中国出口野生水产品的生产企业应当由冰方向中方推荐注册。未经注册，不得向中国出口。
+四、进口产品要求
+冰方应确保输华野生水产品符合以下条件：
+（一）在本国或国际水域合法捕捞或获得。
+（二）原料及产品均未发生以下所列问题：
+1．冰岛已输华或拟输华野生水产品严重违反中国食品安全相关法律法规以及《议定书》规定。
+2．冰岛境内发生《中华人民共和国进境动物检疫疫病名录》（以下简称《名录》）中列明的和世界动物卫生组织（WOAH）规定的必须通报的与《议定书》产品相关的水生动物疫病，已经严重影响输华野生水产品安全。
+3．冰岛境内发生任何与《议定书》相关产品或企业的重大食品安全事件，可能影响输华野生水产品安全。
+（三）未直接或间接使用中国和冰岛禁用的药物或添加剂，按规定使用中国限用或允许使用的药物或添加剂。
+（四）经主管部门检验检疫，未发现中国法律法规中列明的致病微生物、有毒有害物质和异物，未发现《名录》中列明的和WOAH规定的必须通报的任何传染病、寄生虫病和水生动物疫病。
+（五）生产过程（包括捕捞、收货、生产加工、包装、贮存、运输、中转和出口等）均应符合中国安全卫生要求和可追溯要求。
+（六）产品的包装、标签标识应当符合中国食品安全国家标准和要求。
+五、证书要求
+冰方负责按照中方的要求，对输华野生水产品实施检验检疫，并对向中国出口的每批野生水产品出具经双方确认的卫生证书，证明该批产品符合中国食品安全相关法律法规的有关规定。证书至少用中文、英文印制（填写证书时英文为必选语言）。
+卫生证书应完整填写输华野生水产品生产企业的信息。冰方应及时将证书样本和官方印章提供中方备案。如有变更，冰方应至少在生效前一个月向中方备案。
+六、其他要求
+中国海关将依照中国法律法规和《议定书》对输华野生水产品实施检验检疫。
+对于不符合《议定书》要求的产品，实施销毁、退运或其他处理。对产品被发现严重问题或反复违反《议定书》规定的生产企业，中方将采取加强检验检疫或暂停进口等措施。
+特此公告。
+海关总署
+2025年11月13日
+公告下载链接：
+[海关总署关于进口冰岛野生水产品检验和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6825795/2025111713411846036.doc)
+[海关总署关于进口冰岛野生水产品检验和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6825795/2025111713413035792.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6825795/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第211号（关于进口爱沙尼亚野生水产品检验和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕211号 
+【发文机关】海关总署 
+【发布日期】2025-10-27 
+【生效日期】2025-10-27 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第211号（关于进口爱沙尼亚野生水产品检验和卫生要求的公告）
+公告〔2025〕211号 
+根据我国法律法规和中华人民共和国海关总署（以下称中方）与爱沙尼亚共和国地区事务和农业部（以下称爱方）有关爱沙尼亚输华野生水产品的检验和卫生要求规定，即日起，允许符合以下相关要求的爱沙尼亚野生水产品进口：
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
+（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
+（三）《中华人民共和国海关总署与爱沙尼亚共和国地区事务和农业部关于爱沙尼亚输华野生水产品的检验和卫生要求议定书》（以下简称《议定书》）。
+二、进口产品范围
+野生水产品，是指野生的、供人类食用的水生动物产品及其制品、藻类等海洋植物产品及其制品，不包括两栖类、爬行类、水生哺乳动物类、《濒危野生动植物种国际贸易公约》（CITES）附录和中国国家重点保护野生动物名录所列物种、活水生动物及水生动植物繁殖材料。
+三、生产企业要求
+向中国出口野生水产品的生产企业（包括生产、加工、贮存企业），应获爱沙尼亚官方批准并受其有效监督。生产企业的食品安全卫生管理和防护体系应当符合中国食品安全相关法律法规的要求。
+向中国出口野生水产品的生产企业应当由爱方向中方推荐注册。未经注册，不得向中国出口。
+四、进口产品要求
+爱方应确保输华野生水产品符合以下条件：
+（一）在本国或国际水域合法捕捞。
+（二）原料及产品均未发生以下所列问题：
+1．爱沙尼亚已输华或拟输华野生水产品严重违反中国食品安全相关法律法规以及《议定书》规定。
+2．爱沙尼亚境内发生《中华人民共和国进境动物检疫疫病名录》中列明的和世界动物卫生组织（WOAH）规定的必须通报的与本公告产品相关的水生动物疫病，已经严重影响输华野生水产品安全。
+3．爱沙尼亚境内发生重大食品安全事件，或生产企业发生重大公共卫生事件，或捕捞水域受到污染物影响，已经严重影响输华野生水产品安全。
+（三）未直接或间接使用中国禁用的药物或添加剂，按规定使用中国限用或允许使用的药物或添加剂。
+（四）经主管部门检验检疫，未发现中国法律法规中列明的致病微生物、有毒有害物质和异物，以及任何传染病和寄生虫病的病例，未发现《中华人民共和国进境动物检疫疫病名录》中列明的和世界动物卫生组织（WOAH）规定的必须通报的水生动物疫病。
+（五）生产过程（包括捕捞、生产加工、包装、贮存、运输、中转和出口等）均应符合中国相关安全卫生要求和可追溯要求。
+（六）产品的包装、标签标识应当符合中国食品安全国家标准和进口食品安全管理相关规定。
+五、证书要求
+爱方负责按照中方的要求，对输华野生水产品实施检验检疫，并对向中国出口的每批野生水产品出具经双方确认的卫生证书，证明该批产品符合中国食品安全相关法律法规的有关规定。证书至少用中文、英文印制（填写证书时英文为必选语言）。
+卫生证书应完整填写输华野生水产品生产企业的信息。爱方应及时将证书样本和官方印章提供中方备案。如有变更，爱方应至少在生效前一个月向中方备案。
+六、其他要求
+中国海关依照中国相关法律法规及《议定书》对输华野生水产品实施检验检疫。
+对于不合格产品，将依照中国法律法规实施销毁、退运、或其他处理。对发生严重问题或多次发生不合格问题的生产企业，中方可采取加强检验检疫或暂停进口等措施。
+特此公告。
+海关总署
+2025年10月27日
+公告下载链接：
+[海关总署关于进口爱沙尼亚野生水产品检验和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6823152/2025111410263842779.doc)
+[海关总署关于进口爱沙尼亚野生水产品检验和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6823152/2025111410264857017.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6825799/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第225号（关于进口瑞典燕麦植物检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕225号 
+【发文机关】海关总署 
+【发布日期】2025-11-20 
+【生效日期】2025-11-20 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第225号（关于进口瑞典燕麦植物检疫要求的公告）
+公告〔2025〕225号 
+根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与瑞典乡村事务和基础设施部（以下称瑞方）关于瑞典燕麦输华植物检疫要求的规定，即日起，允许符合以下相关要求的瑞典燕麦进口：
+一、检验检疫依据
+（一）《中华人民共和国生物安全法》；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《中华人民共和国食品安全法》及其实施条例；
+（四）《中华人民共和国进出口食品安全管理办法》；
+（五）《中华人民共和国海关总署与瑞典乡村事务和基础设施部关于瑞典燕麦输华植物检疫要求议定书》。
+二、允许进境商品名称
+本公告中燕麦（Avena sativa），是指产自瑞典境内，输往中国用于食用或食品加工用的非种用燕麦籽实。
+三、允许的产地
+瑞典全境。
+四、企业注册
+输华燕麦生产、加工、存放企业应当经中方注册登记，确保其符合中国检验检疫要求。瑞方应提前向中方提交生产、加工、存放企业名单，经中方审核通过后予以注册登记，中方将在海关总署网站上公布相关企业名单。
+五、中方关注的有害生物
+输华燕麦不得携带以下有害生物：
+1．烟草环斑病毒 Tobacco ringspot virus
+2．番茄黑环病毒 Tomato black ring virus
+3．大麦条纹花叶病毒 Barley stripe mosaic virus
+4．豚草Ambrosia artemisiifolia
+5．毒麦 Lolium temulentum
+6．假高粱Sorghum halepense
+7．法国野燕麦Avena ludoviciana
+8．麦角菌Claviceps purpurea
+9．小麦基腐病 Oculimacula yallundae
+10．欧洲麦茎蜂 Cephus pygmeus
+11．黑森瘿蚊 Mayetiola destructor
+12．瑞典麦秆蝇 Oscinella frit
+六、装运前要求
+（一）生产要求。
+1．瑞方应监督企业建立有害生物综合防治体系（IPM），降低中方关注有害生物的发生程度，瑞典爆发中方关注的有害生物或其他危险性有害生物时，瑞方应立即暂停相关地区的燕麦输华，开展调查并采取控制措施。经中方审核认可后，方可恢复输华。
+2．瑞方应对输华燕麦种植、收获、储存、运输等过程进行监管。装运前，企业应采取过筛等清杂措施，确保不带土壤、植物残体、杂草种子及其他外来杂质。
+（二）包装及运输要求。
+1．输华燕麦应使用包装运输，使用的包装应是干净、卫生、透气、新的，符合中国植物检疫和食品安全要求的材料包装。每一包装袋上应以清晰的中文字样标注“本产品输往中华人民共和国”，以及产品名称和生产、加工、存放企业名称及其中方注册号等追溯信息。直接销售的预包装燕麦的包装及标签须符合中国预包装食品包装及标签管理规定（GB 7718）。
+2．输华燕麦运输工具应符合卫生和防疫要求，装运前应进行彻底的检查，防止混入杂草籽、活体昆虫、其他谷物杂质、植物残体、土壤等。
+（三）产品要求。
+输华燕麦应符合中国进境植物检疫和食品安全法律法规、标准要求，不带中方关注的有害生物，不带活虫、螨类、软体动物、土壤、羽毛、动物粪便、杂草种子、枝叶等动植物残体，不得故意添加或混杂其他谷物或外来杂质。
+（四）出口前检验检疫和证书要求。
+出口前，瑞方应对输华燕麦实施检验检疫，对符合要求的燕麦出具植物检疫证书，并在附加声明栏用英文注明：“The consignment is in compliance with the requirements described in the Protocol of Phytosanitary Requirements for the Export of oats from Sweden to China, and is free from any pests concerned by China”（该批货物符合瑞典燕麦输华植物检疫要求议定书要求，不带中方关注的有害生物），同时注明该批货物生产、加工、存放企业名称和中方注册号，以及运输工具编号等追溯信息。发现活虫的货物，应在出口前进行熏蒸处理，处理指标应在植物检疫证书上注明。
+七、进境检验检疫
+（一）证单核查。
+1．核查是否来自注册登记企业；
+2．核查植物检疫证书是否真实有效。
+（二）货物检查。
+根据有关法律法规、行政法规、规章等规定，结合本公告对燕麦实施检验检疫，合格后准予进境。
+（三）不合格处理。
+1．无有效植物检疫证书的，作退回或销毁处理；
+2．来自未经注册登记企业的，作退回或销毁处理；
+3．发现未经中国官方批准的转基因成分的，作退回或销毁处理；
+4．发现活的检疫性有害生物或其他活的有害生物，有有效处理方法的，作除害处理；无有效处理方法的，作退回或销毁处理；
+5．发现其他不符合中国进境动植物检疫和食品安全法律法规和标准要求的，按照相关规定处理。
+发现上述不符合情况，中方将向瑞方通报，并根据严重程度采取暂停相关企业输华资质等措施，直至瑞方采取有效改进措施。
+特此公告。
+海关总署
+2025年11月20日
+公告下载链接：
+[海关总署关于进口瑞典燕麦植物检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6842312/2025112416561950104.doc)
+[海关总署关于进口瑞典燕麦植物检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6842312/2025112416562839115.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6837376/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第222号（关于进口南非鲜食核果检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕222号 
+【发文机关】海关总署 
+【发布日期】2025-11-14 
+【生效日期】2025-11-14 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第222号（关于进口南非鲜食核果检疫要求的公告）
+公告〔2025〕222号 
+根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与南非共和国农业部（以下称南方）有关南非鲜食核果输华植物检疫要求的规定，即日起，允许符合以下相关要求的南非鲜食核果进口。
+一、检疫依据
+（一）《中华人民共和国生物安全法》；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《中华人民共和国食品安全法》及其实施条例；
+（四）《进境水果检验检疫监督管理办法》；
+（五）《中华人民共和国海关总署与南非共和国农业部关于南非鲜食核果输华植物检疫要求议定书》。
+二、允许进境商品名称
+鲜食核果（以下简称核果）包括桃（学名Prunus persica，英文名 Peach）、油桃（学名Prunus persica var. nucipersica，英文名 Nectarine）、李（学名Prunus salicina，英文名 Plum）、杏（Prunus armeniaca，英文名 Apricot）和西梅（学名Prunus domestica，英文名 Prune）。
+三、允许的产地
+南非核果产区。
+四、批准的果园和包装厂
+输华核果果园、包装厂和冷处理设施应经南方审核，并由中方批准注册。注册信息包括名称、地址及注册代码，以便在出口货物不符合本公告相关规定时准确溯源。每年出口季节前，由南方向中方提供注册企业名单，经中方审核批准后在海关总署网站上公布。
+五、中方关注的检疫性有害生物名单
+1．苹果异形小卷蛾 Thaumatotibia leucotreta
+2．地中海实蝇Ceratitis capitata
+3．芒果小条实蝇Ceratitis cosyra
+4．五点小条实蝇Ceratitis quinaria
+5．奎氏实蝇Ceratitis quilicii
+6．纳塔尔小条实蝇Ceratitis rosa
+7．苹果蠹蛾Cydia pomonella
+8．南非麝香石竹卷蛾Epichoristodes acerbella
+9．苹果卷叶蛾Lozotaenia capensana
+10．非洲牡蛎蚧Diaspidiotus africanus
+11．长尾粉蚧Pseudococcus longispinus
+12．梳缺花蓟马Frankliniella schultzei
+13．黑桃短尾蚜Brachycaudus persicae
+14．核果树溃疡病菌Pseudomonas syringae pv. morsprunorum
+15．李类病毒1号Apscaviroid latenspruni (Plum viroid I)
+六、出口前管理
+（一）果园管理。
+1．输华核果果园应在南方监管下建立并实施良好农业操作规范（GAP），包括维持果园卫生条件、及时清理落果等，并执行有害生物综合治理（IPM），如有害生物调查、监测、化学或生物防治以及农事操作等防控措施，避免或最大程度降低核果上发生中方关注的检疫性有害生物。有害生物具体的监测计划和综合管理措施须由南方批准，并应要求向中方提供。
+2．输华果园须由经过南方指导的熟悉植物检疫的技术人员对中方关注的检疫性有害生物开展监测调查，技术人员须通过南方或其授权机构培训。如发现中方关注的检疫性有害生物，应立即采取相应控制措施。
+3．输华果园应保留有害生物监测调查和防治记录至少两年，并应要求向中方提供。有害生物监测及防治记录应当至少包括监测时间、有害生物名称、采取的防治措施；化学防控记录应包括在生长季节内使用的所有化学试剂的名称、活性成分、浓度、施用日期等详细信息。
+4．针对实蝇和苹果异形小卷蛾，输华果园须采取田间综合管理措施，包括开展实蝇（包括地中海实蝇、芒果小条实蝇、奎氏实蝇、五点小条实蝇和纳塔尔小条实蝇）和苹果异形小卷蛾监测诱捕，使用化学防治或生物防治等方法，以降低实蝇和苹果异形小卷蛾种群密度。监测时间应从开花期开始至采收期结束。
+输华果园应使用实蝇诱捕器（如三角型、桶型）开展监测，诱剂需采用经登记的地中海实蝇诱饵。诱捕器密度分别为每平方公里2个（小于1平方公里的果园至少2个诱捕器），每周检查一次诱捕器。如每天每个诱捕器捕获实蝇密度大于0.7，需进行有效防治。
+针对苹果异形小卷蛾，在果园内采用性信息素诱捕进行有害生物监测。诱捕器密度分别为每平方公里2个（小于1平方公里的果园至少2个诱捕器），每周检查1次诱捕器。如发现苹果异形小卷蛾，应立即采取适当的物理、化学或生物防治措施。
+5．针对苹果蠹蛾，在核果产区及相关区域（果园、包装厂以及周围产区）应开展苹果蠹蛾诱捕监测，诱捕器设置密度为每2公顷1个。监测时间从盛花期开始，一直到核果包装工作结束。每2周至少要检查1次诱捕器，诱芯需按使用说明及时更换，如每次检查时，发现诱捕器中的苹果蠹蛾达到3个或以上的，要立即采取防控措施。防控不彻底的果园，将取消本果园出口季的输华资格。
+6．针对核果树溃疡病菌和李类病毒1号等中方关注的病原物，需建立果园监测体系，加强果园管理，在核果产区生长期内，每个月至少开展1次田间监测调查。一旦发现可疑感染症状的，应及时采取样品并送实验室进行分子生物学鉴定。如确认感染上述中方关注的病原物，必须采取综合防治措施控制病原物的发生，防治不彻底的，取消该果园的输华资格。
+7．针对黑桃短尾蚜、非洲牡蛎蚧、南非麝香石竹卷蛾、梳缺花蓟马、苹果卷叶蛾、长尾粉蚧等中方关注的有害生物，需开展监测调查，从花期至收获期结束，每2周至少1次，重点检查果实、果柄、叶等部位。如发现有害生物或其相应危害症状，应及时采取防治措施，以控制有害生物发生或维护有害生物低度流行水平，确保核果果实不带这些检疫性有害生物。
+（二）包装厂管理。
+1．核果加工、包装、储藏和装运过程，须在南方或其授权人员监管下进行。
+2．核果在果实采后加工和包装过程中，应经挑选、分级等工序，以确保不带任何活虫、缺陷果、枝、叶、土壤等。
+3．输华核果的接收、加工、处理、储藏等功能区相对独立、布局合理，且与非输华水果采取隔离措施。
+（三）包装要求。
+1．包装材料应干净卫生、未使用过，符合中国有关植物检疫要求。如使用木质包装，须符合国际植物检疫措施第15号标准（ISPM 15）。
+2．包装好的核果如需存储，应当立即入库并单独存放，避免受到有害生物再次感染。每个包装箱上必须标注水果名称、国家、产地（如区、市或县）、果园注册号、包装厂注册号等信息。每个包装箱和托盘需用中文或英文标出“输往中华人民共和国”或“Exported to the People’s Republic of China”。
+3．装运输华核果的集装箱必须在装箱时检查是否具备良好的卫生条件，装箱时应采取必要的防虫措施。
+（四）检疫处理要求。
+针对实蝇和苹果异形小卷蛾，输华核果应在南方或其授权人员的监管下采取冷处理或熏蒸处理措施。
+冷处理按照出口前冷处理操作程序（见附件1）或运输途中冷处理操作程序（见附件2）进行，处理指标要求如下：-0.6°C或以下（果肉温度），连续处理22天或以上。
+熏蒸处理采用溴甲烷熏蒸剂，处理指标如下：温度在21.1°C或以上，熏蒸剂的剂量为32 g/m3，在正常大气压条件下熏蒸持续时间不低于2 h；且熏蒸期间最低浓度需在0.5 h后不低于26 g/m3，2 h后不低于16 g/m3。
+（五）出口前检验检疫。
+1．南方或其授权人员应按照每批货物2%的比例对每批输华核果进行抽样检查，最小取样量为1200个果实，同时至少对2%样品中的60个果实或检查过程中发现的可疑果进行剖果检查。如两年内没有发生植物检疫问题，抽样比例数可降为1%，但取样量不得少于1200个果实。
+2．如发现中方关注的检疫性有害生物活体，整批货物不得向中国出口。南方应查明原因并采取改进措施，并保存检查记录，应要求提供给中方。
+（六）植物检疫证书要求。
+1．经检疫合格的核果，南方应出具植物检疫证书，注明果园注册号、包装厂注册号以及集装箱号码，并在附加声明中注明：“This consignment complies with the requirements specified in the Protocol of Phytosanitary Requirements for Export of Fresh Stone Fruits from the South Africa to China, and is free from quarantine pests of concern to China.”（该批货物符合南非鲜食核果输华植物检疫议定书要求，不带中方关注的检疫性有害生物。）
+2．对于实施出口前冷处理的，应在植物检疫证书上注明处理温度、持续时间及处理设施名称或编号等信息。对于实施运输途中冷处理的，应在植物检疫证书上标注“Cold treatment in transit”（途中冷处理），并注明处理温度、持续时间、集装箱号码及封识号码等。
+对于实施出口前熏蒸处理的货物，应在植物检疫证书检疫处理栏目内注明熏蒸处理所使用的溴甲烷剂量、持续时间和处理温度及处理设施名称或编号等信息。
+七、进境检验检疫及不合格处理
+输华核果到达中国进境口岸时，中国海关按照以下要求实施检验检疫。
+（一）有关证书和标识核查。
+1．核查进口核果是否获得《进境动植物检疫许可证》。
+2．核查植物检疫证书是否符合本公告第六条第（六）项的规定。
+3．核查包装箱和托盘上的标识是否符合本公告第六条第（三）项的规定。
+4．对于出口前实施冷处理的货物，需核查植物检疫证书、南方签字确认的冷处理结果报告单以及果温探针校正记录等是否满足本公告第六条第（四）项的规定。
+5．对于运输途中实施冷处理的货物，需核查植物检疫证书、冷处理报告、果温探针校正记录等是否满足本公告第六条第（四）项的规定。
+6．对于出口前实施熏蒸处理的货物，需核查植物检疫证书是否满足本公告第六条第（四）项的规定。
+（二）进境检验检疫。
+1．输华核果应从中方允许进口水果的口岸进境。
+2．核果到达中国进境口岸时，中国海关将检查有关单证和标识，并按照中国法律法规和国家标准及本公告要求实施检验检疫。
+（三）不合格处理。
+1．如发现来自未注册的果园、包装厂或处理设施的，则该批货物不准进境。
+2．如冷处理被认定无效或失败，则该批货物将被采取到岸冷处理（可在本集装箱内进行）、退回、销毁等处理措施。
+3．如发现中方关注的检疫性有害生物或南非新发生的检疫性有害生物活体，或土壤，或植物残体等，则该批货物作退回、销毁或除害处理。
+4．如发现不符合中国食品安全法律法规和国家标准的情况，则对该批货物作退回或销毁处理。
+特此公告。
+附件:
+[1.出口前冷处理操作程序.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6825799/2025111713434298440.docx)
+[2.运输途中冷处理操作程序.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6825799/2025111713435247436.docx)
+海关总署
+2025年11月14日
+公告正文下载链接：
+[海关总署关于进口南非鲜食核果检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6825799/2025111713440159521.doc)
+[海关总署关于进口南非鲜食核果检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6825799/2025111713441284641.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6842312/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第227号（关于进口瑞典麦芽检验检疫和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕227号 
+【发文机关】海关总署 
+【发布日期】2025-11-20 
+【生效日期】2025-11-20 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第227号（关于进口瑞典麦芽检验检疫和卫生要求的公告）
+公告〔2025〕227号 
+根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与瑞典乡村事务和基础设施部（以下称瑞方）有关瑞典麦芽输华检验检疫和卫生要求的规定，即日起，允许符合以下相关要求的瑞典麦芽进口。
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
+（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
+（三）《中华人民共和国海关总署与瑞典乡村事务和基础设施部关于瑞典麦芽输华检验检疫和卫生要求议定书》（以下简称《议定书》）。
+二、允许进口产品
+允许进口的麦芽是指以在瑞典种植的大麦（Hordeum vulgare L. ）的成熟果实为原料，在瑞典境内经过发芽、干燥等工艺制成的仅用于食用或食品加工用的产品。
+三、食品安全要求
+输华麦芽应符合中国食品安全和植物检疫相关法律法规、食品安全国家标准以及《议定书》的规定。
+四、植物检疫要求
+（一）输华麦芽应符合中国的植物检疫法律法规。
+（二）输华麦芽不应携带中方关注的检疫性有害生物：谷斑皮蠹Trogoderma granarium。
+（三）输华麦芽不得带有杂草籽、活体昆虫以及故意添加或混杂的其他杂质。
+五、生产企业要求
+瑞方应按中方进口食品境外生产企业注册相关要求对输华麦芽生产、加工、存放单位进行检查，将符合要求的企业推荐给中方注册。企业获得注册后，其产品方可输华。获得注册的瑞典输华麦芽企业名单可通过海关总署网站查询。
+六、原料要求
+输华麦芽的原料应来自经瑞方确认符合相关植物检疫和食品安全要求并予以备案的大麦种植生产企业。
+七、加工过程要求
+瑞方应对输华麦芽的原料种植、生产、加工、储存、运输、出口等过程进行指导和监管，确保符合中国和瑞典的相关食品安全和植物卫生要求，未受到致病微生物或有毒有害物质的污染。
+八、包装、标识要求
+输华麦芽应使用新的、干净、卫生、透气的符合食品安全和植物检疫要求的材料包装，并在运输过程中防止发生撒漏。每一包装应用中文或英文标注“本产品输往中华人民共和国/This product is exported to the People's Republic of China”，以及麦芽的产地、生产加工企业名称及其在华注册号、出口商名称和地址等可追溯信息。上述信息可以以标签形式粘贴在包装上。
+九、运输要求
+装运前，瑞方应对输华麦芽的运输工具进行检查。运输工具应符合卫生要求，不得带有检疫性有害生物或其他限定性检疫物，如杂草籽、活体昆虫、植物残体、土壤以及其他杂质。
+十、植物检疫证书要求
+瑞方应对经检验检疫符合《议定书》要求的输华麦芽出具植物检疫证书。
+输华麦芽植物检疫证书附加声明栏中应注明麦芽生产加工企业名称、在华注册号及“The malt certified by this phytosanitary certificate complies with the phytosanitary provisions of the Protocol on inspection and quarantine requirements for Malt Exported from Sweden to China signed by Sweden and China at Shanghai on November 6th, 2025. The malt is free from any quarantine pests of concern to the China side, such as Trogoderma granarium.”（该植物检疫证书所证明的麦芽符合中瑞双方于2025年11月6日在上海签署的关于瑞典麦芽输华检验检疫和卫生要求议定书的规定。该批货物不带有谷斑皮蠹等中方关注的检疫性有害生物。）
+植物检疫证书内容和格式应事先经双方确认。
+十一、进境检验检疫及不合格处理
+（一）进境检验检疫。输华麦芽到达中国入境口岸后，中国海关将实施检验检疫监管，合格后准予进境。
+（二）不合格处理。中方在输华麦芽中如发现存在违反中国食品安全和植物检疫相关法律法规、食品安全国家标准以及《议定书》规定的情况，中方将按照中国相关法律法规予以处置。
+特此公告。
+海关总署
+2025年11月20日
+公告下载链接：
+[海关总署关于进口瑞典麦芽检验检疫和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6842317/2025112416580628301.doc)
+[海关总署关于进口瑞典麦芽检验检疫和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6842317/2025112416581476290.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6842317/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第226号（关于全面推广报关单证及电子数据自助查询打印的公告）</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕226号 
+【发文机关】海关总署 
+【发布日期】2025-11-21 
+【生效日期】2025-11-21 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第226号（关于全面推广报关单证及电子数据自助查询打印的公告）
+公告〔2025〕226号 
+为进一步优化口岸营商环境，便利企业获取保管期限内的报关单证及数据，在前期开展试点的基础上，海关总署决定全面推广报关单证及电子数据自助查询打印服务。现就有关事宜公告如下：
+一、报关单证及电子数据自助查询打印服务适用范围扩大到全部直属海关。
+二、其他事项按照海关总署公告2025年第146号执行。
+本公告自2025年12月15日起实施。
+特此公告。
+海关总署
+2025年11月21日
+公告下载链接：
+[海关总署关于全面推广报关单证及电子数据自助查询打印的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6842345/2025112417001072279.doc)
+[海关总署关于全面推广报关单证及电子数据自助查询打印的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6842345/2025112417001966203.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6842345/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第231号（关于进口俄罗斯麦麸检验检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕231号 
+【发文机关】海关总署 
+【发布日期】2025-11-27 
+【生效日期】2025-11-27 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第231号（关于进口俄罗斯麦麸检验检疫要求的公告）
+公告〔2025〕231号 
+根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与俄罗斯联邦兽医和植物检疫监督局（以下称俄方）关于俄罗斯麦麸输华卫生与植物卫生要求的规定，即日起，允许符合以下相关要求的俄罗斯麦麸进口：
+一、检验检疫依据
+（一）《中华人民共和国生物安全法》；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《进出口饲料和饲料添加剂检验检疫监督管理办法》；
+（四）《中华人民共和国海关总署与俄罗斯联邦兽医和植物检疫监督局关于俄罗斯麦麸输华卫生与植物卫生要求议定书》。
+二、允许进境商品名称
+本公告所指麦麸（wheat bran），是指在俄罗斯联邦境内种植的小麦籽实，经加工后产生的用于饲用的麸皮副产品，其原料小麦应不带小麦矮腥黑穗病菌（Tilletia controversa J.G. Kuhn）和未经中国官方批准的转基因成分。
+三、企业注册
+输华麦麸应来自俄方考核批准的生产、加工、存放企业。俄方向中方推荐符合要求的生产、加工、存放企业，经中方检查或审查通过后予以注册登记，在海关总署网站上公布并动态更新。
+四、关注的有害生物
+输华麦麸不得携带以下有害生物：
+1．花斑皮蠹Trogoderma variabile
+2．黑斑皮蠹Trogoderma glabrum
+3．拟肾斑皮蠹Trogoderma versicolor
+4．肾斑皮蠹Trogoderma inclusum
+5．条斑皮蠹Trogoderma teukton
+6．褐拟谷盗Tribolium destructor
+7．谷象Sitophilus granarius
+8．毒麦Lolium temulentum
+9．小麦叶疫病菌Alternaria triticina
+10．小麦基腐病菌Oculimacula yallundae
+11．小麦矮腥黑穗病菌Tilletia controversa
+五、装运前要求
+（一）生产要求。
+1．企业应建立相应管理体系及合格供应商筛选制度，建立良好的危害分析和关键控制点（HACCP）体系、溯源管理体系并有效运行，或按照其理念实施管理。
+2．企业应加强对原辅料的生产、加工、仓储、运输等环节的卫生控制，避免被土壤、动物尸体、动物粪便及羽毛等污染，不得添加有毒有害物质和任何动物源性成分，生产设施不得用于动物源性饲料生产。
+3．企业的生产工艺应包含湿热处理，技术要求为：在温度≥85℃、相对湿度≥80%的条件下，湿热处理不低于5分钟。企业应具备霉菌总数、沙门氏菌等安全卫生项目指标的检测能力或委托具备检测能力的机构进行检测。
+4．企业应针对安全卫生项目制定自检自控计划。俄方应对企业实施官方控制，开展每2月不少于1次的官方符合性抽样检测，确保其麦麸符合中国饲料相关安全卫生标准。一旦检出不合格，立即暂停相关企业输华资质并向中方通报，查明原因并采取改进措施。
+（二）包装及运输要求。
+1．俄方应确保输华麦麸使用干净卫生且首次使用的包装袋运输，包装袋上应用中文和英文标注“本产品输往中华人民共和国/This product is for export to the People’s Republic of China”字样，以及产品名称、产地和企业名称及其在华注册编号等信息。
+2．俄方应确保用于运输麦麸的运输工具彻底清扫干净，必要时须进行除害处理。
+3．俄方应确保每批输华麦麸的产品标签符合中国国家标准《饲料标签》（GB 10648）的要求。
+4．输华麦麸应与原料和其他产品分开单独存放，实施物理隔离，采取有效的防鼠、虫、鸟措施，防止污染。
+（三）出口前检验检疫和证书要求。
+出口前，俄方应对输华麦麸实施检验检疫，对符合要求的出具植物检疫证书，并在附加声明中注明“This lot of wheat bran complies with the requirements of the Protocol between the General Administration of Customs of the People’s Republic of China and the Federal Service for Veterinary and Phytosanitary Surveillance (the Russian Federation) on sanitary and phytosanitary requirements for wheat bran exported from the Russian Federation to the People’s Republic of China, and this lot does not contain pests of quarantine importance to the People’s Republic of China”（该批麦麸符合中华人民共和国海关总署与俄罗斯联邦兽医和植物检疫监督局关于俄罗斯麦麸输华卫生与植物卫生要求议定书规定，不携带中方关注的检疫性有害生物），同时注明该批货物生产、加工、存放企业名称及其在华注册编号、集装箱等运输工具编号。出口前或运输途中进行除害处理的，还应注明除害处理方式、处理时间、温度及处理药剂等信息。
+六、进境检验检疫
+（一）证单核查。
+1．核查是否来自注册登记企业。
+2．核查随附的植物检疫证书是否真实有效。
+（二）货物检查。
+根据有关法律法规、行政法规、规章等规定，结合本公告要求，对进境麦麸实施检验检疫，合格后准予进境。
+（三）不符合情况处理。
+1．无有效植物检疫证书的，作退回或销毁处理。
+2．来自未经注册登记企业的，作退回或销毁处理。
+3．发现中方关注的有害生物或其他活的有害生物的，作除害、退回或销毁处理。
+4．发现土壤、未经中国官方批准的转基因成分的，作退回或销毁处理。
+5．发现其他不符合中国进境动植物检疫要求或不符合中国饲料相关安全卫生标准的，将按照相关法律法规规定处理。
+发现上述不合格情况，中方将向俄方通报，并根据不合格情况严重程度采取暂停相关生产企业输华资质，或暂停俄罗斯麦麸输华等措施。
+特此公告。
+海关总署
+2025年11月27日
+公告下载链接：
+[海关总署关于进口俄罗斯麦麸检验检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6854255/2025120115002056822.doc)
+[海关总署关于进口俄罗斯麦麸检验检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6854255/2025120115003083226.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6845264/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第228号（关于进口马耳他野生动物源性水产品检验和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">【法规类型】海关规范性文件 
 【内容类别】其他 
@@ -541,36 +2422,197 @@
 </t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6845264/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6845282/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第233号（关于进口蒙古国蜂蜜检验检疫和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕233号 
+【发文机关】海关总署 
+【发布日期】2025-11-27 
+【生效日期】2025-11-27 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第233号（关于进口蒙古国蜂蜜检验检疫和卫生要求的公告）
+公告〔2025〕233号 
+根据我国相关法律法规与中华人民共和国海关总署（以下称中方）和蒙古国食品、农业和轻工业部（以下称蒙方）有关输华蜂蜜的检验检疫和兽医卫生要求规定，即日起，允许符合相关要求的蒙古国蜂蜜进口。
+一、检验检疫依据
+（一）法律法规。
+《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例，以及《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》等。
+（二）双边议定书。
+《中华人民共和国海关总署和蒙古国食品、农业和轻工业部关于输华蜂蜜检验检疫和兽医卫生要求议定书》（以下简称《议定书》）。
+二、允许输华的产品
+允许输华的蒙古国蜂蜜是指蜜蜂采集植物的花蜜、分泌物或蜜露，与自身分泌物混合后，经充分酿造而成的天然甜物质。
+三、加工企业要求
+输华蜂蜜的加工企业应当经中方注册。蒙方对拟输华蜂蜜加工企业进行审核，认定其符合中国法律法规、标准及《议定书》要求的，向中方推荐。未经注册的蜂蜜加工企业不得向中国出口蜂蜜。
+四、检验检疫要求
+（一）为输华蜂蜜提供原料的蜜蜂须符合下列条件：
+1．来自位于蒙古国境内的养蜂场，该养蜂场应由主管部门登记且受到有效监管。
+2．蜜蜂采集植物的花蜜、分泌物或蜜露应安全无毒，不得来源于有毒蜜源植物和转基因植物。
+（二）蒙方确认其境内无蜂房小甲虫病（蜂窝甲虫）和蜜蜂亮热厉螨病。
+（三）养蜂场周围半径5千米、产品输华前12个月内无美洲蜜蜂幼虫腐臭病和欧洲蜜蜂幼虫腐臭病。
+（四）对于蜜蜂瓦螨病的检疫要求：该批蜂蜜来源养蜂场及其周围半径5千米、产品输华前12个月内无瓦螨侵染；或已使用孔径不超过0.42mm的滤器过滤；或加热至中心温度50℃以上，并在此温度下维持20分钟；或冰冻至中心温度零下12℃或更低温度，并在此温度下维持至少24小时，以确保杀灭蜜蜂瓦螨病及其虫卵，并采取必要措施，有效去除螨虫残体及其虫卵。
+五、生产、贮存和运输要求
+（一）为生产输华蜂蜜提供原料的养蜂场从未使用过中国和蒙古国禁止使用的兽药。
+（二）输华蜂蜜来自已建立溯源系统的加工企业，保证输华蜂蜜可追溯到其养蜂场。
+（三）输华蜂蜜中兽药、农药、微生物、重金属及其他环境污染物残留量不超过中国和蒙古国的最高限量。
+（四）在重大公共卫生疫病流行期间，企业按照有关国际规定和标准，制定必要的蜂蜜安全防控措施，确保蜂蜜在原料接收、加工、包装、贮存、运输等全过程防控措施有效，未被交叉污染。
+（五）输华蜂蜜是卫生、安全的，适合人类食用。
+（六）输华蜂蜜的加工、贮存和运输全过程，均应符合中国和蒙古国的相关卫生要求，防止受有毒有害物质的污染。输华蜂蜜不得与不符合《议定书》要求的产品、非本注册加工企业的产品、本注册加工企业的其他产品同时加工或混合。
+（七）蒙方应做好从养蜂场到加工、包装、贮存各个阶段的标示。应设有专门贮存输华蜂蜜的独立成品库或专门区域并明显标识。
+（八）货物在装入集装箱后，应在蒙方官员监督下加施封识，封识号需在兽医卫生证书中注明。运输过程中不得拆开及更换包装。
+六、证书要求
+输华蜂蜜每一集装箱/批次应至少随附一份正本卫生证书，证明该批次产品符合中国和蒙古国兽医和公共卫生相关法律法规及《议定书》的有关规定。
+兽医卫生证书用中文、蒙古文和英文写成，兽医卫生证书的格式、内容须事先获得双方认可。
+蒙方应提供检验检疫印章印模、封识标志、卫生证书样本、授权签证人员名单及对应的签名式样、防伪标识说明等资料给中方备案，如有更改、变换，至少提前一个月向中方通报。
+七、包装及标识要求
+输华蜂蜜必须用符合中国和蒙古国食品安全国家标准的食品接触材料包装。包装须密封，并应当以中文、蒙古文和英文标明品名、产品的规格、产地（具体到州/省/市）、生产企业注册号、生产批号、目的地（目的地应当标明为中华人民共和国）、生产日期（年/月/日）、保质期等内容。预包装输华蜂蜜还应符合中国关于预包装食品标签的法律法规和标准的要求。
+八、其他要求
+中国海关对输华蜂蜜实施检验检疫。如发现存在违反中国食品安全相关法律法规、食品安全国家标准以及《议定书》规定的情况，中方将按照中国相关法律法规予以处置。
+特此公告。
+海关总署
+2025年11月27日
+公告下载链接：
+[海关总署关于进口蒙古国蜂蜜检验检疫和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6854287/2025120115045359741.doc)
+[海关总署关于进口蒙古国蜂蜜检验检疫和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6854287/2025120115050232284.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6854110/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第232号（关于进口西班牙养殖水产品检验检疫和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕232号 
+【发文机关】海关总署 
+【发布日期】2025-11-27 
+【生效日期】2025-11-27 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第232号（关于进口西班牙养殖水产品检验检疫和卫生要求的公告）
+公告〔2025〕232号 
+根据我国法律法规和中华人民共和国海关总署（以下称中方）与西班牙王国农业、渔业和食品部（以下称西方）有关西班牙输华养殖水产品的检验检疫和卫生要求规定，即日起，允许符合以下相关要求的西班牙养殖水产品进口：
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
+（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
+（三）《中华人民共和国海关总署与西班牙王国农业、渔业和食品部关于西班牙输华养殖水产品的检验检疫和卫生要求议定书》（以下简称《议定书》）。
+二、进口产品范围
+养殖水产品，是指人工养殖的、供人类食用的水生动物产品及其制品、藻类等海洋植物产品及其制品，不包括活水生动物及水生动植物繁殖材料。西班牙输华养殖水产品目录见附件。
+三、生产企业要求
+向中国出口养殖水产品的生产企业（包括养殖场、加工厂、独立冷库），应获西班牙官方批准并受其有效监督。生产企业的食品卫生条件应当符合中国、西班牙食品安全相关法律法规的要求。
+向中国出口养殖水产品的生产企业应当由西方向中方推荐注册。未经注册，不得向中国出口。
+四、进口产品要求
+西方应确保输华养殖水产品符合以下条件：
+（一）在本国水域养殖或来自中国允许进口的国家（地区）。
+（二）原料及产品均未发生以下所列问题：
+1．西班牙已输华或拟输华养殖水产品严重违反中国、西班牙食品安全相关法律法规以及《议定书》规定。
+2．西班牙境内发生《中华人民共和国进境动物检疫疫病名录》（以下简称《名录》）中列明的和世界动物卫生组织（WOAH）规定的必须通报的与本公告产品相关的水生动物疫病，已经严重影响输华养殖水产品安全。
+3．西班牙境内发生重大食品安全事件，或生产企业发生重大公共卫生事件，或养殖区域受到污染物影响，已经影响输华养殖水产品安全。
+（三）未直接或间接使用中国、西班牙禁用的药物或添加剂，按规定使用中方限用或允许使用的药物或添加剂。
+（四）经主管部门检验检疫，未发现中国、西班牙法律法规中列明的致病微生物、有毒有害物质和异物，以及任何传染病和寄生虫病的病例，未发现《名录》中列明的和WOAH规定的必须通报的水生动物疫病。
+（五）生产过程（包括养殖、加工、包装、储存、运输、中转和出口等）均应符合中国相关卫生要求和可追溯要求。
+（六）产品的包装、标签标识应当符合中国食品安全国家标准和进口食品安全管理相关规定。
+五、证书要求
+西方负责按照中方的要求，对输华养殖水产品实施检验检疫，并对向中国出口的每集装箱或每批养殖水产品出具经双方提前确认的卫生证书，证明该批产品符合中国、西班牙食品安全相关法律法规的有关规定。证书至少用中文、英文、西班牙文印制（填写证书时英文为必选语言）。
+卫生证书应完整填写输华养殖水产品生产企业的信息。西方应及时将证书样本、官方印章提供中方备案。如有变更，西方应至少在生效前一个月向中方备案。
+六、其他要求
+中国海关将依照中国法律法规、标准及《议定书》对输华养殖水产品实施检验检疫。对于不合格产品，实施销毁、退运或其他处理。对发生严重问题或多次发生不合格问题的，中方可采取加强检验检疫或暂停进口等措施。
+特此公告。
+附件：[西班牙输华养殖水产品信息表.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6854262/2025120115022524487.docx)
+海关总署
+2025年11月27日
+公告正文下载链接：
+[海关总署关于进口西班牙养殖水产品检验检疫和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6854262/2025120115023984098.doc)
+[海关总署关于进口西班牙养殖水产品检验检疫和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6854262/2025120115025032051.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6854255/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>海关总署公告2025年第229号（关于进口秘鲁鲜食石榴检疫要求的公告）</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
         <is>
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">【法规类型】海关规范性文件 
 【内容类别】其他 
@@ -656,36 +2698,36 @@
 </t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6845282/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6854262/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>海关总署公告2025年第230号（关于进口英国宠物食品检疫和卫生要求的公告）</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">【法规类型】海关规范性文件 
 【内容类别】其他 
@@ -778,351 +2820,36 @@
 </t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6854110/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>海关总署公告2025年第235号（关于启用公自用物品业务电子版单证的公告）</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【法规类型】海关规范性文件 
-【内容类别】其他 
-【文 号】公告〔2025〕235号 
-【发文机关】海关总署 
-【发布日期】2025-12-03 
-【生效日期】2025-12-03 
-【效力】有效 
-【效力说明】
-## 海关总署公告2025年第235号（关于启用公自用物品业务电子版单证的公告）
-公告〔2025〕235号 
-为便利驻华外交机构、进出境人员办理公自用物品进出境手续，以及留学回国人员办理购买国产小汽车手续，海关总署决定启用相关电子版单证，现将有关事项公告如下：
-一、启用电子版《中华人民共和国海关外交公/自用物品进出境申报单》《中华人民共和国海关进出境自用物品申报单》，电子版单证与原纸质版单证样式一致，效力相同。登录国际贸易“单一窗口”平台公自用物品申报模块，应用“综合查询”项下各对应功能，可打印上述电子版单证。
-二、启用电子版《回国人员购买国产汽车准购单》（以下简称《准购单》）供货凭据联和申请人收执联（样张详见附件），取消备案地海关联和监管地海关联，无需与《中华人民共和国海关进出境自用物品申报单》同时使用。回国人员及其代理机构、代理人可登录国际贸易“单一窗口”平台公自用物品申报模块，应用“综合查询”项下“留学生购买国产免税车查询”功能，按业务流程自行打印电子版《准购单》供货凭据联和申请人收执联。汽车生产厂家可应用“综合查询”项下“《准购单》查询”功能核对电子版《准购单》供货凭据联信息。
-本公告自发布之日起施行，此前已开具的纸质版上述单证仍然有效。
-特此公告。
-附件：[中华人民共和国海关回国人员购买国产汽车准购单.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6863278/2025120416325343084.pdf)
-海关总署
-2025年12月3日
-公告正文下载链接：
-[海关总署关于启用公自用物品业务电子版单证的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6863278/%E6%B5%B7%E5%85%B3%E6%80%BB%E7%BD%B2%E5%85%B3%E4%BA%8E%E5%90%AF%E7%94%A8%E5%85%AC%E8%87%AA%E7%94%A8%E7%89%A9%E5%93%81%E4%B8%9A%E5%8A%A1%E7%94%B5%E5%AD%90%E7%89%88%E5%8D%95%E8%AF%81%E7%9A%84%E5%85%AC%E5%91%8A.doc)
-[海关总署关于启用公自用物品业务电子版单证的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6863278/%E6%B5%B7%E5%85%B3%E6%80%BB%E7%BD%B2%E5%85%B3%E4%BA%8E%E5%90%AF%E7%94%A8%E5%85%AC%E8%87%AA%E7%94%A8%E7%89%A9%E5%93%81%E4%B8%9A%E5%8A%A1%E7%94%B5%E5%AD%90%E7%89%88%E5%8D%95%E8%AF%81%E7%9A%84%E5%85%AC%E5%91%8A.pdf)
-</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6854255/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>海关总署公告2025年第232号（关于进口西班牙养殖水产品检验检疫和卫生要求的公告）</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【法规类型】海关规范性文件 
-【内容类别】其他 
-【文 号】公告〔2025〕232号 
-【发文机关】海关总署 
-【发布日期】2025-11-27 
-【生效日期】2025-11-27 
-【效力】有效 
-【效力说明】
-## 海关总署公告2025年第232号（关于进口西班牙养殖水产品检验检疫和卫生要求的公告）
-公告〔2025〕232号 
-根据我国法律法规和中华人民共和国海关总署（以下称中方）与西班牙王国农业、渔业和食品部（以下称西方）有关西班牙输华养殖水产品的检验检疫和卫生要求规定，即日起，允许符合以下相关要求的西班牙养殖水产品进口：
-一、检验检疫依据
-（一）《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例。
-（二）《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》。
-（三）《中华人民共和国海关总署与西班牙王国农业、渔业和食品部关于西班牙输华养殖水产品的检验检疫和卫生要求议定书》（以下简称《议定书》）。
-二、进口产品范围
-养殖水产品，是指人工养殖的、供人类食用的水生动物产品及其制品、藻类等海洋植物产品及其制品，不包括活水生动物及水生动植物繁殖材料。西班牙输华养殖水产品目录见附件。
-三、生产企业要求
-向中国出口养殖水产品的生产企业（包括养殖场、加工厂、独立冷库），应获西班牙官方批准并受其有效监督。生产企业的食品卫生条件应当符合中国、西班牙食品安全相关法律法规的要求。
-向中国出口养殖水产品的生产企业应当由西方向中方推荐注册。未经注册，不得向中国出口。
-四、进口产品要求
-西方应确保输华养殖水产品符合以下条件：
-（一）在本国水域养殖或来自中国允许进口的国家（地区）。
-（二）原料及产品均未发生以下所列问题：
-1．西班牙已输华或拟输华养殖水产品严重违反中国、西班牙食品安全相关法律法规以及《议定书》规定。
-2．西班牙境内发生《中华人民共和国进境动物检疫疫病名录》（以下简称《名录》）中列明的和世界动物卫生组织（WOAH）规定的必须通报的与本公告产品相关的水生动物疫病，已经严重影响输华养殖水产品安全。
-3．西班牙境内发生重大食品安全事件，或生产企业发生重大公共卫生事件，或养殖区域受到污染物影响，已经影响输华养殖水产品安全。
-（三）未直接或间接使用中国、西班牙禁用的药物或添加剂，按规定使用中方限用或允许使用的药物或添加剂。
-（四）经主管部门检验检疫，未发现中国、西班牙法律法规中列明的致病微生物、有毒有害物质和异物，以及任何传染病和寄生虫病的病例，未发现《名录》中列明的和WOAH规定的必须通报的水生动物疫病。
-（五）生产过程（包括养殖、加工、包装、储存、运输、中转和出口等）均应符合中国相关卫生要求和可追溯要求。
-（六）产品的包装、标签标识应当符合中国食品安全国家标准和进口食品安全管理相关规定。
-五、证书要求
-西方负责按照中方的要求，对输华养殖水产品实施检验检疫，并对向中国出口的每集装箱或每批养殖水产品出具经双方提前确认的卫生证书，证明该批产品符合中国、西班牙食品安全相关法律法规的有关规定。证书至少用中文、英文、西班牙文印制（填写证书时英文为必选语言）。
-卫生证书应完整填写输华养殖水产品生产企业的信息。西方应及时将证书样本、官方印章提供中方备案。如有变更，西方应至少在生效前一个月向中方备案。
-六、其他要求
-中国海关将依照中国法律法规、标准及《议定书》对输华养殖水产品实施检验检疫。对于不合格产品，实施销毁、退运或其他处理。对发生严重问题或多次发生不合格问题的，中方可采取加强检验检疫或暂停进口等措施。
-特此公告。
-附件：[西班牙输华养殖水产品信息表.docx](http://www.customs.gov.cn/customs/302249/302266/302267/6854262/2025120115022524487.docx)
-海关总署
-2025年11月27日
-公告正文下载链接：
-[海关总署关于进口西班牙养殖水产品检验检疫和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6854262/2025120115023984098.doc)
-[海关总署关于进口西班牙养殖水产品检验检疫和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6854262/2025120115025032051.pdf)
-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6854262/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>海关总署公告2025年第231号（关于进口俄罗斯麦麸检验检疫要求的公告）</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【法规类型】海关规范性文件 
-【内容类别】其他 
-【文 号】公告〔2025〕231号 
-【发文机关】海关总署 
-【发布日期】2025-11-27 
-【生效日期】2025-11-27 
-【效力】有效 
-【效力说明】
-## 海关总署公告2025年第231号（关于进口俄罗斯麦麸检验检疫要求的公告）
-公告〔2025〕231号 
-根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与俄罗斯联邦兽医和植物检疫监督局（以下称俄方）关于俄罗斯麦麸输华卫生与植物卫生要求的规定，即日起，允许符合以下相关要求的俄罗斯麦麸进口：
-一、检验检疫依据
-（一）《中华人民共和国生物安全法》；
-（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
-（三）《进出口饲料和饲料添加剂检验检疫监督管理办法》；
-（四）《中华人民共和国海关总署与俄罗斯联邦兽医和植物检疫监督局关于俄罗斯麦麸输华卫生与植物卫生要求议定书》。
-二、允许进境商品名称
-本公告所指麦麸（wheat bran），是指在俄罗斯联邦境内种植的小麦籽实，经加工后产生的用于饲用的麸皮副产品，其原料小麦应不带小麦矮腥黑穗病菌（Tilletia controversa J.G. Kuhn）和未经中国官方批准的转基因成分。
-三、企业注册
-输华麦麸应来自俄方考核批准的生产、加工、存放企业。俄方向中方推荐符合要求的生产、加工、存放企业，经中方检查或审查通过后予以注册登记，在海关总署网站上公布并动态更新。
-四、关注的有害生物
-输华麦麸不得携带以下有害生物：
-1．花斑皮蠹Trogoderma variabile
-2．黑斑皮蠹Trogoderma glabrum
-3．拟肾斑皮蠹Trogoderma versicolor
-4．肾斑皮蠹Trogoderma inclusum
-5．条斑皮蠹Trogoderma teukton
-6．褐拟谷盗Tribolium destructor
-7．谷象Sitophilus granarius
-8．毒麦Lolium temulentum
-9．小麦叶疫病菌Alternaria triticina
-10．小麦基腐病菌Oculimacula yallundae
-11．小麦矮腥黑穗病菌Tilletia controversa
-五、装运前要求
-（一）生产要求。
-1．企业应建立相应管理体系及合格供应商筛选制度，建立良好的危害分析和关键控制点（HACCP）体系、溯源管理体系并有效运行，或按照其理念实施管理。
-2．企业应加强对原辅料的生产、加工、仓储、运输等环节的卫生控制，避免被土壤、动物尸体、动物粪便及羽毛等污染，不得添加有毒有害物质和任何动物源性成分，生产设施不得用于动物源性饲料生产。
-3．企业的生产工艺应包含湿热处理，技术要求为：在温度≥85℃、相对湿度≥80%的条件下，湿热处理不低于5分钟。企业应具备霉菌总数、沙门氏菌等安全卫生项目指标的检测能力或委托具备检测能力的机构进行检测。
-4．企业应针对安全卫生项目制定自检自控计划。俄方应对企业实施官方控制，开展每2月不少于1次的官方符合性抽样检测，确保其麦麸符合中国饲料相关安全卫生标准。一旦检出不合格，立即暂停相关企业输华资质并向中方通报，查明原因并采取改进措施。
-（二）包装及运输要求。
-1．俄方应确保输华麦麸使用干净卫生且首次使用的包装袋运输，包装袋上应用中文和英文标注“本产品输往中华人民共和国/This product is for export to the People’s Republic of China”字样，以及产品名称、产地和企业名称及其在华注册编号等信息。
-2．俄方应确保用于运输麦麸的运输工具彻底清扫干净，必要时须进行除害处理。
-3．俄方应确保每批输华麦麸的产品标签符合中国国家标准《饲料标签》（GB 10648）的要求。
-4．输华麦麸应与原料和其他产品分开单独存放，实施物理隔离，采取有效的防鼠、虫、鸟措施，防止污染。
-（三）出口前检验检疫和证书要求。
-出口前，俄方应对输华麦麸实施检验检疫，对符合要求的出具植物检疫证书，并在附加声明中注明“This lot of wheat bran complies with the requirements of the Protocol between the General Administration of Customs of the People’s Republic of China and the Federal Service for Veterinary and Phytosanitary Surveillance (the Russian Federation) on sanitary and phytosanitary requirements for wheat bran exported from the Russian Federation to the People’s Republic of China, and this lot does not contain pests of quarantine importance to the People’s Republic of China”（该批麦麸符合中华人民共和国海关总署与俄罗斯联邦兽医和植物检疫监督局关于俄罗斯麦麸输华卫生与植物卫生要求议定书规定，不携带中方关注的检疫性有害生物），同时注明该批货物生产、加工、存放企业名称及其在华注册编号、集装箱等运输工具编号。出口前或运输途中进行除害处理的，还应注明除害处理方式、处理时间、温度及处理药剂等信息。
-六、进境检验检疫
-（一）证单核查。
-1．核查是否来自注册登记企业。
-2．核查随附的植物检疫证书是否真实有效。
-（二）货物检查。
-根据有关法律法规、行政法规、规章等规定，结合本公告要求，对进境麦麸实施检验检疫，合格后准予进境。
-（三）不符合情况处理。
-1．无有效植物检疫证书的，作退回或销毁处理。
-2．来自未经注册登记企业的，作退回或销毁处理。
-3．发现中方关注的有害生物或其他活的有害生物的，作除害、退回或销毁处理。
-4．发现土壤、未经中国官方批准的转基因成分的，作退回或销毁处理。
-5．发现其他不符合中国进境动植物检疫要求或不符合中国饲料相关安全卫生标准的，将按照相关法律法规规定处理。
-发现上述不合格情况，中方将向俄方通报，并根据不合格情况严重程度采取暂停相关生产企业输华资质，或暂停俄罗斯麦麸输华等措施。
-特此公告。
-海关总署
-2025年11月27日
-公告下载链接：
-[海关总署关于进口俄罗斯麦麸检验检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6854255/2025120115002056822.doc)
-[海关总署关于进口俄罗斯麦麸检验检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6854255/2025120115003083226.pdf)
-</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>http://www.customs.gov.cn/customs/302249/302266/302267/6854287/index.html</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>海关总署公告2025年第233号（关于进口蒙古国蜂蜜检验检疫和卫生要求的公告）</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【法规类型】海关规范性文件 
-【内容类别】其他 
-【文 号】公告〔2025〕233号 
-【发文机关】海关总署 
-【发布日期】2025-11-27 
-【生效日期】2025-11-27 
-【效力】有效 
-【效力说明】
-## 海关总署公告2025年第233号（关于进口蒙古国蜂蜜检验检疫和卫生要求的公告）
-公告〔2025〕233号 
-根据我国相关法律法规与中华人民共和国海关总署（以下称中方）和蒙古国食品、农业和轻工业部（以下称蒙方）有关输华蜂蜜的检验检疫和兽医卫生要求规定，即日起，允许符合相关要求的蒙古国蜂蜜进口。
-一、检验检疫依据
-（一）法律法规。
-《中华人民共和国食品安全法》及其实施条例、《中华人民共和国进出境动植物检疫法》及其实施条例、《中华人民共和国进出口商品检验法》及其实施条例，以及《中华人民共和国进出口食品安全管理办法》《中华人民共和国进口食品境外生产企业注册管理规定》等。
-（二）双边议定书。
-《中华人民共和国海关总署和蒙古国食品、农业和轻工业部关于输华蜂蜜检验检疫和兽医卫生要求议定书》（以下简称《议定书》）。
-二、允许输华的产品
-允许输华的蒙古国蜂蜜是指蜜蜂采集植物的花蜜、分泌物或蜜露，与自身分泌物混合后，经充分酿造而成的天然甜物质。
-三、加工企业要求
-输华蜂蜜的加工企业应当经中方注册。蒙方对拟输华蜂蜜加工企业进行审核，认定其符合中国法律法规、标准及《议定书》要求的，向中方推荐。未经注册的蜂蜜加工企业不得向中国出口蜂蜜。
-四、检验检疫要求
-（一）为输华蜂蜜提供原料的蜜蜂须符合下列条件：
-1．来自位于蒙古国境内的养蜂场，该养蜂场应由主管部门登记且受到有效监管。
-2．蜜蜂采集植物的花蜜、分泌物或蜜露应安全无毒，不得来源于有毒蜜源植物和转基因植物。
-（二）蒙方确认其境内无蜂房小甲虫病（蜂窝甲虫）和蜜蜂亮热厉螨病。
-（三）养蜂场周围半径5千米、产品输华前12个月内无美洲蜜蜂幼虫腐臭病和欧洲蜜蜂幼虫腐臭病。
-（四）对于蜜蜂瓦螨病的检疫要求：该批蜂蜜来源养蜂场及其周围半径5千米、产品输华前12个月内无瓦螨侵染；或已使用孔径不超过0.42mm的滤器过滤；或加热至中心温度50℃以上，并在此温度下维持20分钟；或冰冻至中心温度零下12℃或更低温度，并在此温度下维持至少24小时，以确保杀灭蜜蜂瓦螨病及其虫卵，并采取必要措施，有效去除螨虫残体及其虫卵。
-五、生产、贮存和运输要求
-（一）为生产输华蜂蜜提供原料的养蜂场从未使用过中国和蒙古国禁止使用的兽药。
-（二）输华蜂蜜来自已建立溯源系统的加工企业，保证输华蜂蜜可追溯到其养蜂场。
-（三）输华蜂蜜中兽药、农药、微生物、重金属及其他环境污染物残留量不超过中国和蒙古国的最高限量。
-（四）在重大公共卫生疫病流行期间，企业按照有关国际规定和标准，制定必要的蜂蜜安全防控措施，确保蜂蜜在原料接收、加工、包装、贮存、运输等全过程防控措施有效，未被交叉污染。
-（五）输华蜂蜜是卫生、安全的，适合人类食用。
-（六）输华蜂蜜的加工、贮存和运输全过程，均应符合中国和蒙古国的相关卫生要求，防止受有毒有害物质的污染。输华蜂蜜不得与不符合《议定书》要求的产品、非本注册加工企业的产品、本注册加工企业的其他产品同时加工或混合。
-（七）蒙方应做好从养蜂场到加工、包装、贮存各个阶段的标示。应设有专门贮存输华蜂蜜的独立成品库或专门区域并明显标识。
-（八）货物在装入集装箱后，应在蒙方官员监督下加施封识，封识号需在兽医卫生证书中注明。运输过程中不得拆开及更换包装。
-六、证书要求
-输华蜂蜜每一集装箱/批次应至少随附一份正本卫生证书，证明该批次产品符合中国和蒙古国兽医和公共卫生相关法律法规及《议定书》的有关规定。
-兽医卫生证书用中文、蒙古文和英文写成，兽医卫生证书的格式、内容须事先获得双方认可。
-蒙方应提供检验检疫印章印模、封识标志、卫生证书样本、授权签证人员名单及对应的签名式样、防伪标识说明等资料给中方备案，如有更改、变换，至少提前一个月向中方通报。
-七、包装及标识要求
-输华蜂蜜必须用符合中国和蒙古国食品安全国家标准的食品接触材料包装。包装须密封，并应当以中文、蒙古文和英文标明品名、产品的规格、产地（具体到州/省/市）、生产企业注册号、生产批号、目的地（目的地应当标明为中华人民共和国）、生产日期（年/月/日）、保质期等内容。预包装输华蜂蜜还应符合中国关于预包装食品标签的法律法规和标准的要求。
-八、其他要求
-中国海关对输华蜂蜜实施检验检疫。如发现存在违反中国食品安全相关法律法规、食品安全国家标准以及《议定书》规定的情况，中方将按照中国相关法律法规予以处置。
-特此公告。
-海关总署
-2025年11月27日
-公告下载链接：
-[海关总署关于进口蒙古国蜂蜜检验检疫和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6854287/2025120115045359741.doc)
-[海关总署关于进口蒙古国蜂蜜检验检疫和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6854287/2025120115050232284.pdf)
-</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6863271/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>海关总署公告2025年第234号（关于进口秘鲁鲜食香蕉检疫要求的公告）</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">【法规类型】海关规范性文件 
 【内容类别】其他 
@@ -1199,36 +2926,260 @@
 </t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6863271/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第235号（关于启用公自用物品业务电子版单证的公告）</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕235号 
+【发文机关】海关总署 
+【发布日期】2025-12-03 
+【生效日期】2025-12-03 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第235号（关于启用公自用物品业务电子版单证的公告）
+公告〔2025〕235号 
+为便利驻华外交机构、进出境人员办理公自用物品进出境手续，以及留学回国人员办理购买国产小汽车手续，海关总署决定启用相关电子版单证，现将有关事项公告如下：
+一、启用电子版《中华人民共和国海关外交公/自用物品进出境申报单》《中华人民共和国海关进出境自用物品申报单》，电子版单证与原纸质版单证样式一致，效力相同。登录国际贸易“单一窗口”平台公自用物品申报模块，应用“综合查询”项下各对应功能，可打印上述电子版单证。
+二、启用电子版《回国人员购买国产汽车准购单》（以下简称《准购单》）供货凭据联和申请人收执联（样张详见附件），取消备案地海关联和监管地海关联，无需与《中华人民共和国海关进出境自用物品申报单》同时使用。回国人员及其代理机构、代理人可登录国际贸易“单一窗口”平台公自用物品申报模块，应用“综合查询”项下“留学生购买国产免税车查询”功能，按业务流程自行打印电子版《准购单》供货凭据联和申请人收执联。汽车生产厂家可应用“综合查询”项下“《准购单》查询”功能核对电子版《准购单》供货凭据联信息。
+本公告自发布之日起施行，此前已开具的纸质版上述单证仍然有效。
+特此公告。
+附件：[中华人民共和国海关回国人员购买国产汽车准购单.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6863278/2025120416325343084.pdf)
+海关总署
+2025年12月3日
+公告正文下载链接：
+[海关总署关于启用公自用物品业务电子版单证的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6863278/%E6%B5%B7%E5%85%B3%E6%80%BB%E7%BD%B2%E5%85%B3%E4%BA%8E%E5%90%AF%E7%94%A8%E5%85%AC%E8%87%AA%E7%94%A8%E7%89%A9%E5%93%81%E4%B8%9A%E5%8A%A1%E7%94%B5%E5%AD%90%E7%89%88%E5%8D%95%E8%AF%81%E7%9A%84%E5%85%AC%E5%91%8A.doc)
+[海关总署关于启用公自用物品业务电子版单证的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6863278/%E6%B5%B7%E5%85%B3%E6%80%BB%E7%BD%B2%E5%85%B3%E4%BA%8E%E5%90%AF%E7%94%A8%E5%85%AC%E8%87%AA%E7%94%A8%E7%89%A9%E5%93%81%E4%B8%9A%E5%8A%A1%E7%94%B5%E5%AD%90%E7%89%88%E5%8D%95%E8%AF%81%E7%9A%84%E5%85%AC%E5%91%8A.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>http://www.customs.gov.cn/customs/302249/302266/302267/6863278/index.html</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第240号（关于2026年中国海关统计数据公布时间的公告）</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕240号 
+【发文机关】海关总署 
+【发布日期】2025-12-05 
+【生效日期】2025-12-05 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第240号（关于2026年中国海关统计数据公布时间的公告）
+公告〔2025〕240号 
+为满足社会公众对海关统计数据的使用需求，根据《中华人民共和国海关统计条例》有关规定，现公布《2026年中国海关统计数据公布时间表》（见附件）。
+特此公告。
+附件： [2026年中国海关统计数据公布时间表.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6875716/2025121108240732700.doc)
+海关总署
+2025年12月5日
+公告正文下载链接：
+[海关总署关于2026年中国海关统计数据公布时间的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6875716/2025121108241779910.doc)
+[海关总署关于2026年中国海关统计数据公布时间的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6875716/2025121108242649248.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6863474/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第238号（关于进一步明确境内承运海关监管货物的运输企业及其运输工具管理事项的公告）</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕238号 
+【发文机关】海关总署 
+【发布日期】2025-12-04 
+【生效日期】2025-12-10 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第238号（关于进一步明确境内承运海关监管货物的运输企业及其运输工具管理事项的公告）
+公告〔2025〕238号 
+为进一步优化境内公路/水运承运海关监管货物的运输企业及其车辆/船舶备案管理，现将有关事项公告如下：
+一、在国际贸易“单一窗口”上线转关备案申请功能，境内承运海关监管货物的运输企业可以在线办理本企业及其运输工具备案、变更、注销申请等相关业务。因海关监管需要，或者因系统故障等原因无法正常传输相关电子数据的，企业应提供纸质单证资料。涉及相关法律文书格式文本详见附件1和附件2。涉及相关数据项填制条件和填制规范详见附件3、附件4和附件5。
+二、本公告自2025年12月10日起施行。海关总署公告2018年第103号、2022年第73号所附的法律文书格式文本与本公告不一致的，以本公告为准。
+特此公告。
+附件：
+[1.境内公路承运海关监管货物的运输企业及其车辆备案管理涉及法律文书格式文本.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514271280887.doc)
+[2.境内水运承运海关监管货物的运输企业及其船舶备案管理涉及法律文书格式文本.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514271957173.doc)
+[3.境内公路承运海关监管货物运输企业及其运输工具备案数据项.xls](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514272888757.xls)
+[4.境内水运承运海关监管货物运输企业及其运输工具备案数据项.xlsx](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514273650225.xlsx)
+[5.境内承运海关监管货物运输企业及其运输工具备案数据项填制规范.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514274580099.doc)
+海关总署
+2025年12月4日
+公告正文下载链接：
+[海关总署关于进一步明确境内承运海关监管货物的运输企业及其运输工具管理事项的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514275322620.doc)
+[海关总署关于进一步明确境内承运海关监管货物的运输企业及其运输工具管理事项的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514280193753.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6865969/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>海关总署 农业农村部公告2025年第241号（关于防止新加坡新城疫传入我国的公告）</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】知识产权类 
+【文 号】公告〔2025〕241号 
+【发文机关】海关总署 农业农村部 
+【发布日期】2025-12-05 
+【生效日期】2025-12-05 
+【效力】有效 
+【效力说明】
+## 海关总署 农业农村部公告2025年第241号（关于防止新加坡新城疫传入我国的公告）
+公告〔2025〕241号 
+近日，世界动物卫生组织（WOAH）发布信息，新加坡发生新城疫疫情。为防止疫情传入，保护我国畜牧业安全和生物安全，根据相关法律法规，现公告如下：
+一、禁止直接或间接从新加坡输入禽及相关产品（源于禽未经加工或者虽经加工但仍有可能传播疫病的产品）。
+二、禁止寄递或携带来自新加坡的禽及相关产品入境。一经发现一律作退回或销毁处理。
+三、来自新加坡的进境运输工具上卸下的动植物性废弃物、泔水等，一律在海关的监督下作除害处理，不得擅自抛弃。
+四、对边防检查等部门截获的非法入境的来自新加坡的禽及相关产品，一律在海关的监督下作销毁处理。
+五、凡违反上述规定者，由海关依照《中华人民共和国海关法》、《中华人民共和国生物安全法》、《中华人民共和国进出境动植物检疫法》及其实施条例有关规定处理。
+六、各级海关、各级农业农村部门要分别按照《中华人民共和国海关法》《中华人民共和国生物安全法》《中华人民共和国进出境动植物检疫法》《中华人民共和国动物防疫法》等有关规定，密切配合，做好检疫、防疫和监督工作。
+本公告自发布之日起实施。
+特此公告。
+海关总署 农业农村部
+2025年12月5日
+公告下载链接：
+[海关总署 农业农村部关于防止新加坡新城疫传入我国的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6875720/2025121108260772617.doc)
+[海关总署 农业农村部关于防止新加坡新城疫传入我国的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6875720/2025121108261871591.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6865971/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>海关总署公告2025年第236号（关于进口土耳其养殖和野生水产品检验和卫生要求的公告）</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">【法规类型】海关规范性文件 
 【内容类别】其他 
@@ -1280,36 +3231,36 @@
 </t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6863474/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6866912/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>海关总署 国家卫生健康委 市场监管总局 国家药监局公告2025年第237号（关于试点实施进口食药物质分类管理措施的公告）</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
         <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">【法规类型】海关规范性文件 
 【内容类别】其他 
@@ -1338,300 +3289,36 @@
 </t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6865969/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>海关总署 农业农村部公告2025年第241号（关于防止新加坡新城疫传入我国的公告）</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【法规类型】海关规范性文件 
-【内容类别】知识产权类 
-【文 号】公告〔2025〕241号 
-【发文机关】海关总署 农业农村部 
-【发布日期】2025-12-05 
-【生效日期】2025-12-05 
-【效力】有效 
-【效力说明】
-## 海关总署 农业农村部公告2025年第241号（关于防止新加坡新城疫传入我国的公告）
-公告〔2025〕241号 
-近日，世界动物卫生组织（WOAH）发布信息，新加坡发生新城疫疫情。为防止疫情传入，保护我国畜牧业安全和生物安全，根据相关法律法规，现公告如下：
-一、禁止直接或间接从新加坡输入禽及相关产品（源于禽未经加工或者虽经加工但仍有可能传播疫病的产品）。
-二、禁止寄递或携带来自新加坡的禽及相关产品入境。一经发现一律作退回或销毁处理。
-三、来自新加坡的进境运输工具上卸下的动植物性废弃物、泔水等，一律在海关的监督下作除害处理，不得擅自抛弃。
-四、对边防检查等部门截获的非法入境的来自新加坡的禽及相关产品，一律在海关的监督下作销毁处理。
-五、凡违反上述规定者，由海关依照《中华人民共和国海关法》、《中华人民共和国生物安全法》、《中华人民共和国进出境动植物检疫法》及其实施条例有关规定处理。
-六、各级海关、各级农业农村部门要分别按照《中华人民共和国海关法》《中华人民共和国生物安全法》《中华人民共和国进出境动植物检疫法》《中华人民共和国动物防疫法》等有关规定，密切配合，做好检疫、防疫和监督工作。
-本公告自发布之日起实施。
-特此公告。
-海关总署 农业农村部
-2025年12月5日
-公告下载链接：
-[海关总署 农业农村部关于防止新加坡新城疫传入我国的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6875720/2025121108260772617.doc)
-[海关总署 农业农村部关于防止新加坡新城疫传入我国的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6875720/2025121108261871591.pdf)
-</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6865971/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>海关总署公告2025年第238号（关于进一步明确境内承运海关监管货物的运输企业及其运输工具管理事项的公告）</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6875716/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第239号（关于进口卢旺达鲜食鳄梨检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
         <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【法规类型】海关规范性文件 
-【内容类别】其他 
-【文 号】公告〔2025〕238号 
-【发文机关】海关总署 
-【发布日期】2025-12-04 
-【生效日期】2025-12-10 
-【效力】有效 
-【效力说明】
-## 海关总署公告2025年第238号（关于进一步明确境内承运海关监管货物的运输企业及其运输工具管理事项的公告）
-公告〔2025〕238号 
-为进一步优化境内公路/水运承运海关监管货物的运输企业及其车辆/船舶备案管理，现将有关事项公告如下：
-一、在国际贸易“单一窗口”上线转关备案申请功能，境内承运海关监管货物的运输企业可以在线办理本企业及其运输工具备案、变更、注销申请等相关业务。因海关监管需要，或者因系统故障等原因无法正常传输相关电子数据的，企业应提供纸质单证资料。涉及相关法律文书格式文本详见附件1和附件2。涉及相关数据项填制条件和填制规范详见附件3、附件4和附件5。
-二、本公告自2025年12月10日起施行。海关总署公告2018年第103号、2022年第73号所附的法律文书格式文本与本公告不一致的，以本公告为准。
-特此公告。
-附件：
-[1.境内公路承运海关监管货物的运输企业及其车辆备案管理涉及法律文书格式文本.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514271280887.doc)
-[2.境内水运承运海关监管货物的运输企业及其船舶备案管理涉及法律文书格式文本.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514271957173.doc)
-[3.境内公路承运海关监管货物运输企业及其运输工具备案数据项.xls](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514272888757.xls)
-[4.境内水运承运海关监管货物运输企业及其运输工具备案数据项.xlsx](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514273650225.xlsx)
-[5.境内承运海关监管货物运输企业及其运输工具备案数据项填制规范.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514274580099.doc)
-海关总署
-2025年12月4日
-公告正文下载链接：
-[海关总署关于进一步明确境内承运海关监管货物的运输企业及其运输工具管理事项的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514275322620.doc)
-[海关总署关于进一步明确境内承运海关监管货物的运输企业及其运输工具管理事项的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6865971/2025120514280193753.pdf)
-</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6866912/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>海关总署公告2025年第240号（关于2026年中国海关统计数据公布时间的公告）</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【法规类型】海关规范性文件 
-【内容类别】其他 
-【文 号】公告〔2025〕240号 
-【发文机关】海关总署 
-【发布日期】2025-12-05 
-【生效日期】2025-12-05 
-【效力】有效 
-【效力说明】
-## 海关总署公告2025年第240号（关于2026年中国海关统计数据公布时间的公告）
-公告〔2025〕240号 
-为满足社会公众对海关统计数据的使用需求，根据《中华人民共和国海关统计条例》有关规定，现公布《2026年中国海关统计数据公布时间表》（见附件）。
-特此公告。
-附件： [2026年中国海关统计数据公布时间表.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6875716/2025121108240732700.doc)
-海关总署
-2025年12月5日
-公告正文下载链接：
-[海关总署关于2026年中国海关统计数据公布时间的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6875716/2025121108241779910.doc)
-[海关总署关于2026年中国海关统计数据公布时间的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6875716/2025121108242649248.pdf)
-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6875716/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>海关总署公告2025年第242号（关于进口俄罗斯绿豆植物检疫要求的公告）</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【法规类型】海关规范性文件 
-【内容类别】其他 
-【文 号】公告〔2025〕242号 
-【发文机关】海关总署 
-【发布日期】2025-12-09 
-【生效日期】2025-12-09 
-【效力】有效 
-【效力说明】
-## 海关总署公告2025年第242号（关于进口俄罗斯绿豆植物检疫要求的公告）
-公告〔2025〕242号 
-根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与俄罗斯联邦兽医和植物检疫监督局（以下称俄方）关于俄罗斯绿豆输华植物检疫要求的规定，即日起，允许符合以下相关要求的俄罗斯绿豆进口：
-一、检验检疫依据
-（一）《中华人民共和国生物安全法》；
-（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
-（三）《中华人民共和国食品安全法》及其实施条例；
-（四）《中华人民共和国进出口食品安全管理办法》；
-（五）《中华人民共和国海关总署与俄罗斯联邦兽医和植物检疫监督局关于俄罗斯绿豆输华植物检疫要求议定书》。
-二、允许进口商品名称
-本公告中的绿豆（Vigna radiata），是指在俄罗斯联邦境内种植和加工，输往中国用于食用或食品加工用的非种用绿豆籽实。
-三、允许的产地
-俄罗斯联邦全境。
-四、企业注册
-输华绿豆的生产、加工、存放企业应当经俄方考核批准，由俄方向中方推荐符合要求的企业，经中方检查或审查通过后予以注册登记，中方将在海关总署网站上公布相关企业名单并动态更新。
-五、中方关注的检疫性有害生物
-输华绿豆不得携带以下检疫性有害生物：
-1．四纹豆象 Callosobruchus maculatus
-2．灰豆象 Callosobruchus phaseoli
-3．番茄斑萎病毒 Tomato spotted wilt virus
-4．菜豆细菌性萎蔫病菌 Curtobacterium flaccumfaciens pv. flaccumfaciens
-5．菜豆晕疫病菌 Pseudomonas savastanoi pv.phaseolicola
-6．豌豆脚腐病菌 Didymella pinodella
-7．棉花黄萎病菌 Verticillium dahliae
-六、装运前要求
-（一）生产要求。
-1．俄方应按照国际植物保护公约和国际植物检疫措施标准要求，在种植和仓储区域对中方关注的检疫性有害生物进行监测，并根据中方需要提交监测报告。
-2．俄方应监督绿豆的种植、收获、加工、仓储、运输和出口过程，确保其具备完整的可追溯体系。俄方应督促企业对输华绿豆实施严格的筛选除杂，确保不带畸形、破碎、病变粒以及昆虫、螨类、软体动物、土壤、杂草籽及其他植物残体。
-3．俄方在绿豆上发现新的中方关注的检疫性有害生物时，应及时向中方通报，并采取有效防控措施。
-（二）包装及运输要求。
-输华绿豆应使用包装运输，使用的包装应是全新、清洁、透气的材料。每个包装应以清晰的中文和英文标注“本产品输往中华人民共和国/This product is for export to the People’s Republic of China”字样，以及产品名称、产地和生产、加工、存放企业名称及其在华注册编号等信息。直接销售的预包装绿豆的包装及标签须符合中国预包装食品包装及标签管理规定（GB 7718）。以上内容应采用标签形式粘贴于包装上。
-（三）产品要求。
-输华绿豆应符合中国进境植物检疫和食品安全法律法规要求，不带中方关注的检疫性有害生物、土壤、活体昆虫、杂草种子、其他谷物或植物残体和砂砾等异物。
-（四）出口前检验检疫和证书要求。
-出口前，俄方应对输华绿豆实施植物检疫监督及质量安全监测，对符合要求的绿豆出具植物检疫证书，并在附加声明栏注明“This lot of mung beans complies with the requirements of the Protocol between the General Administration of Customs of the People’s Republic of China and the Federal Service for Veterinary and Phytosanitary Surveillance (the Russian Federation) on the phytosanitary requirements for mung beans exported from the Russian Federation to the People’s Republic of China, and this lot does not contain pests of quarantine importance to the People’s Republic of China”（该批绿豆符合中华人民共和国海关总署与俄罗斯联邦兽医和植物检疫监督局关于俄罗斯绿豆输华植物检疫要求议定书的规定，不带中方关注的检疫性有害生物），同时还应注明该批货物的生产、加工、存放企业名称及其在华注册编号，以及集装箱号等运输工具编号。发现活虫的货物，应在出口前进行检疫处理，植物检疫证书中应注明处理方法、时间、温度和药剂等信息。
-七、进境检验检疫
-（一）证单核查。
-1．核查是否来自注册登记企业。
-2．核查植物检疫证书是否真实有效。
-（二）货物检查。
-根据有关法律、行政法规、规章等规定，结合本公告第五条、第六条对输华绿豆实施检验检疫，合格后准予进境。
-（三）不合格处理。
-1．无有效植物检疫证书的，作退回或销毁处理。
-2．来自未经注册登记企业的，作退回或销毁处理。
-3．发现活的检疫性有害生物或其他活的有害生物，有有效处理方法的，作除害处理；无有效处理方法的，作退回或销毁处理。
-4．发现其他不符合中国进境动植物检疫和食品安全法律法规、标准要求的，按照相关规定处理。
-发现上述不符合情况，中方将向俄方通报，并根据严重程度采取暂停相关企业输华资质等措施，直至俄方采取有效改进措施。
-特此公告。
-海关总署
-2025年12月9日
-公告下载链接：
-[海关总署关于进口俄罗斯绿豆植物检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6875744/2025121108274679560.doc)
-[海关总署关于进口俄罗斯绿豆植物检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6875744/2025121108275556833.pdf)
-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6875720/index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>海关总署公告2025年第239号（关于进口卢旺达鲜食鳄梨检疫要求的公告）</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>有效</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>规范性文件</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">【法规类型】海关规范性文件 
 【内容类别】其他 
@@ -1715,9 +3402,510 @@
 </t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6875720/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第242号（关于进口俄罗斯绿豆植物检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕242号 
+【发文机关】海关总署 
+【发布日期】2025-12-09 
+【生效日期】2025-12-09 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第242号（关于进口俄罗斯绿豆植物检疫要求的公告）
+公告〔2025〕242号 
+根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与俄罗斯联邦兽医和植物检疫监督局（以下称俄方）关于俄罗斯绿豆输华植物检疫要求的规定，即日起，允许符合以下相关要求的俄罗斯绿豆进口：
+一、检验检疫依据
+（一）《中华人民共和国生物安全法》；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《中华人民共和国食品安全法》及其实施条例；
+（四）《中华人民共和国进出口食品安全管理办法》；
+（五）《中华人民共和国海关总署与俄罗斯联邦兽医和植物检疫监督局关于俄罗斯绿豆输华植物检疫要求议定书》。
+二、允许进口商品名称
+本公告中的绿豆（Vigna radiata），是指在俄罗斯联邦境内种植和加工，输往中国用于食用或食品加工用的非种用绿豆籽实。
+三、允许的产地
+俄罗斯联邦全境。
+四、企业注册
+输华绿豆的生产、加工、存放企业应当经俄方考核批准，由俄方向中方推荐符合要求的企业，经中方检查或审查通过后予以注册登记，中方将在海关总署网站上公布相关企业名单并动态更新。
+五、中方关注的检疫性有害生物
+输华绿豆不得携带以下检疫性有害生物：
+1．四纹豆象 Callosobruchus maculatus
+2．灰豆象 Callosobruchus phaseoli
+3．番茄斑萎病毒 Tomato spotted wilt virus
+4．菜豆细菌性萎蔫病菌 Curtobacterium flaccumfaciens pv. flaccumfaciens
+5．菜豆晕疫病菌 Pseudomonas savastanoi pv.phaseolicola
+6．豌豆脚腐病菌 Didymella pinodella
+7．棉花黄萎病菌 Verticillium dahliae
+六、装运前要求
+（一）生产要求。
+1．俄方应按照国际植物保护公约和国际植物检疫措施标准要求，在种植和仓储区域对中方关注的检疫性有害生物进行监测，并根据中方需要提交监测报告。
+2．俄方应监督绿豆的种植、收获、加工、仓储、运输和出口过程，确保其具备完整的可追溯体系。俄方应督促企业对输华绿豆实施严格的筛选除杂，确保不带畸形、破碎、病变粒以及昆虫、螨类、软体动物、土壤、杂草籽及其他植物残体。
+3．俄方在绿豆上发现新的中方关注的检疫性有害生物时，应及时向中方通报，并采取有效防控措施。
+（二）包装及运输要求。
+输华绿豆应使用包装运输，使用的包装应是全新、清洁、透气的材料。每个包装应以清晰的中文和英文标注“本产品输往中华人民共和国/This product is for export to the People’s Republic of China”字样，以及产品名称、产地和生产、加工、存放企业名称及其在华注册编号等信息。直接销售的预包装绿豆的包装及标签须符合中国预包装食品包装及标签管理规定（GB 7718）。以上内容应采用标签形式粘贴于包装上。
+（三）产品要求。
+输华绿豆应符合中国进境植物检疫和食品安全法律法规要求，不带中方关注的检疫性有害生物、土壤、活体昆虫、杂草种子、其他谷物或植物残体和砂砾等异物。
+（四）出口前检验检疫和证书要求。
+出口前，俄方应对输华绿豆实施植物检疫监督及质量安全监测，对符合要求的绿豆出具植物检疫证书，并在附加声明栏注明“This lot of mung beans complies with the requirements of the Protocol between the General Administration of Customs of the People’s Republic of China and the Federal Service for Veterinary and Phytosanitary Surveillance (the Russian Federation) on the phytosanitary requirements for mung beans exported from the Russian Federation to the People’s Republic of China, and this lot does not contain pests of quarantine importance to the People’s Republic of China”（该批绿豆符合中华人民共和国海关总署与俄罗斯联邦兽医和植物检疫监督局关于俄罗斯绿豆输华植物检疫要求议定书的规定，不带中方关注的检疫性有害生物），同时还应注明该批货物的生产、加工、存放企业名称及其在华注册编号，以及集装箱号等运输工具编号。发现活虫的货物，应在出口前进行检疫处理，植物检疫证书中应注明处理方法、时间、温度和药剂等信息。
+七、进境检验检疫
+（一）证单核查。
+1．核查是否来自注册登记企业。
+2．核查植物检疫证书是否真实有效。
+（二）货物检查。
+根据有关法律、行政法规、规章等规定，结合本公告第五条、第六条对输华绿豆实施检验检疫，合格后准予进境。
+（三）不合格处理。
+1．无有效植物检疫证书的，作退回或销毁处理。
+2．来自未经注册登记企业的，作退回或销毁处理。
+3．发现活的检疫性有害生物或其他活的有害生物，有有效处理方法的，作除害处理；无有效处理方法的，作退回或销毁处理。
+4．发现其他不符合中国进境动植物检疫和食品安全法律法规、标准要求的，按照相关规定处理。
+发现上述不符合情况，中方将向俄方通报，并根据严重程度采取暂停相关企业输华资质等措施，直至俄方采取有效改进措施。
+特此公告。
+海关总署
+2025年12月9日
+公告下载链接：
+[海关总署关于进口俄罗斯绿豆植物检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6875744/2025121108274679560.doc)
+[海关总署关于进口俄罗斯绿豆植物检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6875744/2025121108275556833.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>http://www.customs.gov.cn/customs/302249/302266/302267/6875744/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第243号（关于中国与新加坡原产地电子联网升级有关事宜的公告）</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕243号 
+【发文机关】海关总署 
+【发布日期】2025-12-10 
+【生效日期】2025-12-11 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第243号（关于中国与新加坡原产地电子联网升级有关事宜的公告）
+公告〔2025〕243号 
+为进一步便利自由贸易协定项下货物的合规通关，自2025年12月11日起，“中国—新加坡原产地电子信息交换系统”升级功能上线运行，在原有实时传输《中华人民共和国政府和新加坡共和国政府自由贸易协定》（以下简称《中新自贸协定》）、《中国—东盟全面经济合作框架协议》（以下简称《中国东盟框架协议》）项下新加坡海关签发的有关原产地证书和流动证明，以及经新加坡中转货物的未再加工证明电子数据的基础上，新增实时传输《区域全面经济伙伴关系协定》（RCEP）项下新加坡海关签发的原产地证书电子数据。现就有关事宜公告如下：
+一、进口货物收货人或者其代理人（以下简称进口人）在货物进口时凭新加坡签发的原产地证书申请享受RCEP、《中国东盟框架协议》或者《中新自贸协定》项下协定税率的，按照海关总署公告2021年第34号规定选择“通关无纸化”方式申报时，无需通过“优惠贸易协定原产地要素申报系统”填报原产地证明电子数据和直接运输规则承诺事项，也无需以电子方式上传原产地证书。
+选择“通关无纸化”方式申报时，对于系统提示“无法查找到原产地证明电子数据”的，自2025年12月11日至2026年2月28日期间，进口人可以按照海关总署公告2021年第34号的有关规定，通过“优惠贸易协定原产地要素申报系统”录入原产地证书电子信息和直接运输规则承诺事项，并以电子方式上传原产地证书；自2026年3月1日起，对于系统提示“无法查找到原产地证明电子数据”的，进口人应当按规定申请办理相应税款担保手续，后续可通过中国海关原产地服务平台“联网原产地证书状态查询”功能确认原产地证书电子数据传输情况，按规定解除税款担保手续。
+二、进口人选择“有纸报关”方式申报的，在申报进口时应当提交原产地证书纸质文件。
+本公告自2025年12月11日起实施。
+特此公告。
+海关总署
+2025年12月10日
+公告下载链接：
+[海关总署关于中国与新加坡原产地电子联网升级有关事宜的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6884100/2025121510193649712.doc)
+[海关总署关于中国与新加坡原产地电子联网升级有关事宜的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6884100/2025121510194686770.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6884100/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>海关总署 农业农村部公告2025年第224号（关于解除波兰高致病性禽流感疫情禁令的公告）</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】知识产权类 
+【文 号】公告〔2025〕224号 
+【发文机关】海关总署 农业农村部 
+【发布日期】2025-10-31 
+【生效日期】2025-10-31 
+【效力】有效 
+【效力说明】
+## 海关总署 农业农村部公告2025年第224号（关于解除波兰高致病性禽流感疫情禁令的公告）
+公告〔2025〕224号 
+根据风险分析结果，自本公告发布之日起，允许波兰符合高致病性禽流感、新城疫区域化和生物安全隔离区划及检验检疫要求的禽类及其产品输华。
+海关总署、农业农村部2024年联合公告第113号同时废止。
+特此公告。
+海关总署 农业农村部
+2025年10月31日
+公告下载链接：
+[海关总署 农业农村部关于解除波兰高致病性禽流感疫情禁令的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6884173/2025121510285218010.doc)
+[海关总署 农业农村部关于解除波兰高致病性禽流感疫情禁令的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6884173/2025121510290091217.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6884132/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第246号（关于发布《出口食品微生物学检验通则》等117项行业标准的公告）</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕246号 
+【发文机关】海关总署 
+【发布日期】2025-12-11 
+【生效日期】2025-12-11 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第246号（关于发布《出口食品微生物学检验通则》等117项行业标准的公告）
+公告〔2025〕246号 
+现发布《出口食品微生物学检验通则》等117项行业标准（目录见附件）。《出口食品微生物学检验通则》（SN/T 0330—2012）等12项行业标准自新标准实施之日起废止。
+本次发布的标准文本可通过中国技术性贸易措施网站（http://www.tbtsps.cn）标准栏目查阅。
+特此公告。
+附件：[《出口食品微生物学检验通则》等117项行业标准目录.xls](http://www.customs.gov.cn/customs/302249/302266/302267/6884132/2025121510213135253.xls)
+海关总署
+2025年12月11日
+公告正文下载链接：
+[海关总署关于发布《出口食品微生物学检验通则》等117项行业标准的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6884132/2025121510214247356.doc)
+[海关总署关于发布《出口食品微生物学检验通则》等117项行业标准的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6884132/2025121510215095299.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6884136/index.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第244号（关于进口老挝鲜食榴莲植物检疫要求的公告）</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>规范性文件</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】海关规范性文件 
+【内容类别】其他 
+【文 号】公告〔2025〕244号 
+【发文机关】海关总署 
+【发布日期】2025-12-12 
+【生效日期】2025-12-12 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第244号（关于进口老挝鲜食榴莲植物检疫要求的公告）
+公告〔2025〕244号 
+根据我国相关法律法规和中华人民共和国海关总署（以下称中方）与老挝人民民主共和国农业与环境部（以下称老方）有关老挝鲜食榴莲输华植物检疫要求的规定，即日起，允许符合以下相关要求的老挝鲜食榴莲进口。
+一、检验检疫依据
+（一）《中华人民共和国生物安全法》；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《中华人民共和国食品安全法》及其实施条例；
+（四）《进境水果检验检疫监督管理办法》；
+（五）《中华人民共和国海关总署与老挝人民民主共和国农业与环境部关于老挝鲜食榴莲输华植物检疫要求议定书》。
+二、允许进境商品名称
+鲜食榴莲（学名Durio zibethinus Murray，英文名Durian，以下简称榴莲）。
+三、允许的产地
+老挝榴莲产区。
+四、批准的果园和包装厂
+输华榴莲的果园、包装厂须经老方审核，并由中方批准注册，注册信息包括名称、地址及注册号码，以便在出口货物不符合本公告相关规定时准确溯源。每年出口季前，由老方向中方提供注册企业名单，经中方审核批准后在海关总署网站上公布。
+五、中方关注的检疫性有害生物名单
+1．番石榴果实蝇 Bactrocera correcta
+2．榴莲果核夜蛾 Mudaria luteileprosa
+3．杰克贝尔氏粉蚧 Pseudococcus jackbeardsley
+4．南洋臀纹粉蚧 Planococcus lilacinus
+5．大洋臀纹粉蚧 Planococcus minor
+六、出口前管理
+（一）果园管理。
+1．输华果园应在老方监管下建立完善的质量管理体系和溯源体系，实施良好农业操作规范（GAP），维持果园卫生条件，如周围无影响水果生产的污染源、及时清理坏果、落果和烂果等；并应实施有害生物综合治理（IPM），包括定期开展有害生物监测，物理、化学或生物防治有害生物，以及农事操作等防控措施。
+2．老方应按国际植物检疫措施标准第6号（ISPM 6）的要求，针对中方关注的检疫性有害生物制定管理计划，组织实施果园监测。如在监测中发现有害生物或其相应症状，采取包括化学、物理或生物防治在内的综合管理措施，以确保输华榴莲不带中方关注的检疫性有害生物。
+3．有害生物的监测与防治应在专业技术人员指导下实施。技术人员应当接受老方或其授权机构培训。
+4．所有注册果园必须保留有害生物的监测和防治记录，并应中方要求予以提供。防治记录应包括生长季节使用的所有化学药剂名称、有效成分、使用剂量及使用日期等详细信息。
+5．针对番石榴果实蝇，输华果园应从开花期至收获期，使用诱捕器开展实蝇监测。诱捕器密度为每公顷1个，面积小于3公顷的果园至少安装3个诱捕器，每两周检查一次。一旦监测到实蝇，须进行有效防治，防治不彻底的果园，禁止出口。
+6．针对榴莲果核夜蛾，输华果园应在整个生长期定期开展监测，重点检查果实表面是否有虫孔，如有虫孔，应及时采取剖果检查虫卵、幼虫及为害情况。此外，还需在果园内采用灯诱、性信息素诱捕等方式进行有害生物监测。一旦发现榴莲果核夜蛾，应立即采取适当的物理、化学或生物防治措施进行根除。
+7．针对杰克贝尔氏粉蚧、南洋臀纹粉蚧和大洋臀纹粉蚧等有害生物，从榴莲开花期至收获期，果园每两周进行一次监测，检查果实、茎、枝和叶上是否有介壳虫发生。除视觉检查外，还应该在枝条、茎杆处采用多种物理或化学方法监测有害生物，一旦发现应进行有效防治。
+（二）包装厂管理。
+1．输华榴莲的加工、包装、储藏和装运过程，须在老方或其授权官员监管下进行。
+2．输华榴莲的包装厂应整洁卫生，地面需硬化，且有原料场和成品库。
+3．输华榴莲的存放、加工、处理、储藏等功能区应相对独立、布局合理，且与生活区采取隔离措施并有适当的距离。
+4．输华榴莲在包装过程中，应经人工挑选、分级和清洁等工序，剔除病果、虫果、烂果、畸形果、枝叶或其他植物残体及土壤等，并采用高压气枪或水枪吹喷和刷洗等有效措施清洁果实表面，必要时可用细软干净的棉布对榴莲外表进行手工擦拭，以有效去除果实表面附着的介壳虫、虫卵、病原孢子等。此外，如有必要应在包装厂内进行杀虫处理。
+5．包装过程应符合中国食品安全法律法规和国家标准，不得违法添加非食用物质。
+6．包装好的榴莲如需存储，应当立即入库并单独存放，避免受到有害生物再次感染。
+7．装有输华榴莲的集装箱在装箱时必须检查并确保具备良好的卫生条件。
+8．注册包装厂应建立溯源体系以保证输华榴莲可追溯至注册果园，记录包括加工包装日期、来源果园名称或其注册号码、生产量、出口日期、出口数量、输往国家、集装箱号码等信息。
+（三）包装要求。
+1．输华榴莲包装材料应干净卫生、未使用过，符合中国有关植物检疫要求。如使用木质包装，须符合国际植物检疫措施标准第15号（ISPM 15）要求。
+2．每个包装箱上应用中文或英文标注水果名称、产地（省、市、区）、出口国家、果园名称或其注册号码、包装厂名称或其注册号码等信息。每个包装箱和托盘需用中文或英文标注“输往中华人民共和国”或“Exported to the People’s Republic of China”。
+（四）出口前检验检疫。
+1．在贸易开始的前两年内，老方应按照每批输华榴莲2%的比例进行抽样检查。若两年内未发生植物检疫问题，抽样比例可降为1%。
+2．如发现中方关注的检疫性有害生物或枝叶、土壤，整批货物不得出口中国。老方应查明原因，并采取改进措施。同时，保存查获记录，并应要求提供给中方。
+（五）植物检疫证书要求。
+1．经检疫合格的货物，老方应按照国际植物检疫措施标准第12号（ISPM12）出具植物检疫证书，注明果园和包装厂名称或注册号码，并填写以下附加声明：“This consignment complies with requirements specified in the Protocol of Phytosanitary Requirements for Export of Fresh Durian from Lao PDR to China, and is free from any quarantine pests of concern to China.”（该批货物符合老挝鲜食榴莲输华植物检疫议定书要求，不带中方关注的检疫性有害生物。）
+2．在榴莲输华贸易开始前，老方应向中方提供植物检疫证书样本，以便确认和备案。
+七、进境检验检疫及不合格处理
+输华榴莲到达中国进境口岸时，中国海关将按照以下要求实施检验检疫。
+（一）有关证书和标识核查。
+1．核查进口榴莲是否获得进境动植物检疫许可证。
+2．核查植物检疫证书是否符合本公告第六条第（五）项的规定。
+3．核查包装箱和托盘上的标识是否符合本公告第六条第（三）项的规定。
+（二）进境检验检疫。
+1．输华榴莲应从中方允许进口水果的口岸进境。
+2．根据有关法律、行政法规、规章等规定及本公告要求对进口榴莲实施检验检疫，经检验检疫合格的，准予进境。
+（三）不合格处理。
+1．如发现来自未经批准的果园、包装厂，则该批货物不准进境。
+2．如发现中方关注的检疫性有害生物或老挝新发生的其他有害生物活体，或发现土壤、植物残体等，则对该批货物作退回、销毁或除害处理。
+3．如果发现不符合中国食品安全法律法规和国家标准的，则对该批货物作退回或销毁处理。
+特此公告。
+海关总署
+2025年12月12日
+公告下载链接：
+[海关总署关于进口老挝鲜食榴莲植物检疫要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6884136/2025121510235641051.doc)
+[海关总署关于进口老挝鲜食榴莲植物检疫要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6884136/2025121510240626815.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6884173/index.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>文号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>发布日期</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>实施日期</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>效力</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>法规类型</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>主体内容</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>海关总署公告2025年第206号（关于进口乌兹别克斯坦樱桃干检验检疫和卫生要求的公告）</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【法规类型】
+【内容类别】
+【文 号】公告〔2025〕206号 
+【发文机关】海关总署 
+【发布日期】2025-10-28 
+【生效日期】2025-10-28 
+【效力】有效 
+【效力说明】
+## 海关总署公告2025年第206号（关于进口乌兹别克斯坦樱桃干检验检疫和卫生要求的公告）
+公告〔2025〕206号 
+根据我国法律法规和中华人民共和国海关总署（以下称中方）与乌兹别克斯坦共和国农业部（以下称乌方）有关乌兹别克斯坦樱桃干输华检验检疫和卫生要求的规定，即日起，允许符合以下要求的乌兹别克斯坦樱桃干进口。
+一、检验检疫依据
+（一）《中华人民共和国食品安全法》及其实施条例；
+（二）《中华人民共和国进出境动植物检疫法》及其实施条例；
+（三）《中华人民共和国进出口商品检验法》及其实施条例；
+（四）《中华人民共和国进出口食品安全管理办法》；
+（五）《中华人民共和国海关总署与乌兹别克斯坦共和国农业部关于乌兹别克斯坦樱桃干输华检验检疫和卫生要求议定书》（以下简称《议定书》）。
+二、允许进口的产品
+允许进口的樱桃干，是指由乌兹别克斯坦共和国境内种植的蔷薇科（Rosaceae）李属（Prunus L.）多年生木本植物樱桃树（Prunus pseudocerasus Lindl.）的果实为原料，在乌兹别克斯坦境内经清洗、干燥、分选等加工工艺制成的可供人类食用的干制樱桃产品。
+三、食品安全要求
+乌兹别克斯坦输华樱桃干应符合中国食品安全和植物检疫相关法律法规、食品安全国家标准以及《议定书》的规定。
+四、植物检疫要求
+（一）输华樱桃干不得带有以下中方关注的检疫性有害生物：欧洲樱桃实蝇（Rhagoletis cerasi)、葡萄花翅小卷蛾（Lobesia botrana）、霍氏长盾蚧（Mercetaspis halli）、榆蛎蚧（Lepidosaphesulmi）、大丽花轮枝孢（Verticillium dahliae）、丁香假单胞菌丁香致病变种（Pseudomonas syringae pv. syringae）。
+（二）输华樱桃干不得带有活虫、虫卵、土壤，不得混有杂草种子、植物残体、金属异物和砂砾等杂质。
+（三）输华樱桃干在出口前应进行熏蒸处理，以保证干果中不带有活的昆虫。
+五、企业要求
+乌方应按中方进口食品境外生产企业注册相关要求对乌兹别克斯坦输华樱桃干生产、加工、存放单位进行检查，将符合中方要求的企业推荐给中方注册。中方对符合要求的企业予以注册。企业获得注册后，其产品方可输华。获得注册的乌兹别克斯坦共和国输华樱桃干企业名单可通过海关总署网站查询。
+六、原料要求
+输华樱桃干的原料应来自经乌方确认符合相关植物检疫和食品安全要求的樱桃种植企业。
+七、加工过程要求
+乌方应对输华樱桃干的原料种植、生产、加工、储存、运输、出口等过程进行指导和监管，确保符合中国和乌兹别克斯坦的相关食品安全和植物卫生要求，防止受到致病微生物或有毒有害物质的污染。
+八、包装、标识要求
+输华樱桃干应使用干净、卫生、透气、新的符合食品安全和植物检疫要求的材料包装，并在运输过程中防止发生撒漏。每一包装应以中文或英文标注“本产品输往中华人民共和国/This product is exported to the People's Republic of China”，以及樱桃干的品名、产地、生产加工企业名称及其在华注册编号、出口商名称和地址等可追溯信息。上述信息可以以标签形式粘贴在包装上。
+九、运输要求
+装运前，乌方应对输华樱桃干的运输工具进行检查。运输工具应符合卫生要求，不得带有检疫性有害生物或其他限定性检疫物，如杂草籽、活体昆虫、植物残体、土壤以及其他杂质。
+十、证书要求
+出口前，乌方应对经检验检疫符合《议定书》要求的输华樱桃干出具植物检疫证书。证书附加声明栏中应注明樱桃干生产加工企业名称、在华注册编号及“The dried cherries certified by this phytosanitary certificate comply with the provisions of the Protocol on inspection, quarantine and sanitary requirements for dried cherries to be exported from Uzbekistan to China signed on October 14th,2025 by China and Uzbekistan. The dried cherries are free from Rhagoletis ceras, Lobesia botrana, Mercetaspis halli, Lepidosaphesulmi, Verticillium dahliae and Pseudomonas syringae pv. syringae, and other quarantine pests of concern by the Chinese side.”（该植物检疫证书所证明的樱桃干符合中乌双方于2025年10月14日签署的关于乌兹别克斯坦樱桃干输华检验检疫和卫生要求议定书的规定。该批货物不带有欧洲樱桃实蝇（Rhagoletis cerasi）、葡萄花翅小卷蛾（Lobesia botrana）、霍氏长盾蚧（Mercetaspis halli）、榆蛎蚧（Lepidosaphesulmi）、大丽花轮枝孢（Verticillium dahliae）、丁香假单胞菌丁香致病变种（Pseudomonas syringae pv. syringae）等中方关注的检疫性有害生物）。
+检疫处理方法（如药剂、温度、时间和其他技术要求）应在植物检疫证书中注明。
+十一、进境检验检疫及不合格处理
+（一）进境检验检疫。输华樱桃干到达中国入境口岸后，中国海关将实施检验检疫监管，合格后准予进境。
+（二）不合格处理。中方在输华樱桃干中如发现存在违反中国食品安全和植物检疫相关法律法规、食品安全国家标准以及《议定书》规定的情况，中方将按照中国相关法律法规予以处置。
+特此公告。
+海关总署
+2025年10月28日
+公告下载链接：
+[海关总署关于进口乌兹别克斯坦樱桃干检验检疫和卫生要求的公告.doc](http://www.customs.gov.cn/customs/302249/302266/302267/6800375/2025103109230542173.doc)
+[海关总署关于进口乌兹别克斯坦樱桃干检验检疫和卫生要求的公告.pdf](http://www.customs.gov.cn/customs/302249/302266/302267/6800375/2025103109231428363.pdf)
+</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>http://www.customs.gov.cn/customs/302249/302266/302267/6800372/index.html</t>
         </is>
       </c>
     </row>
